--- a/resources/TIER/TIER_version_4_NOV_2025.xlsx
+++ b/resources/TIER/TIER_version_4_NOV_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/resources/TIER/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{B91578D5-1F77-794E-821E-7EC860824472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B82B818-7B76-2A4B-97A1-AFCBE024A9E6}"/>
   <bookViews>
-    <workbookView xWindow="-29380" yWindow="-5300" windowWidth="28620" windowHeight="17500" firstSheet="2" activeTab="4" xr2:uid="{1A5468E0-6E35-4542-9FB0-87A161045F3B}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" firstSheet="2" activeTab="6" xr2:uid="{1A5468E0-6E35-4542-9FB0-87A161045F3B}"/>
   </bookViews>
   <sheets>
     <sheet name="OVERVIEW - Read this" sheetId="2" r:id="rId1"/>
@@ -4369,29 +4369,14 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -4402,14 +4387,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4428,6 +4413,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4480,11 +4480,23 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -4519,23 +4531,23 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4555,33 +4567,6 @@
     <xf numFmtId="0" fontId="34" fillId="10" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4597,6 +4582,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4605,6 +4599,12 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -5005,6 +5005,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -5503,8 +5507,8 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="217"/>
-      <c r="B3" s="219"/>
+      <c r="A3" s="212"/>
+      <c r="B3" s="214"/>
       <c r="C3" s="224"/>
       <c r="D3" s="16" t="str">
         <f>'Scenario overview'!B6</f>
@@ -5522,7 +5526,7 @@
         <f>'Scenario overview'!B9</f>
         <v>A low-burden country achieving one or more of the 95s</v>
       </c>
-      <c r="H3" s="221"/>
+      <c r="H3" s="216"/>
       <c r="I3" s="235"/>
       <c r="J3" s="235"/>
       <c r="K3" s="235"/>
@@ -5557,7 +5561,7 @@
       <c r="M4" s="239"/>
     </row>
     <row r="5" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="207" t="s">
+      <c r="A5" s="220" t="s">
         <v>250</v>
       </c>
       <c r="B5" s="73" t="s">
@@ -5593,8 +5597,8 @@
       <c r="N5" s="59"/>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="208"/>
-      <c r="B6" s="203" t="s">
+      <c r="A6" s="221"/>
+      <c r="B6" s="209" t="s">
         <v>256</v>
       </c>
       <c r="C6" s="80" t="s">
@@ -5629,8 +5633,8 @@
       <c r="N6" s="59"/>
     </row>
     <row r="7" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="208"/>
-      <c r="B7" s="212"/>
+      <c r="A7" s="221"/>
+      <c r="B7" s="207"/>
       <c r="C7" s="66" t="s">
         <v>260</v>
       </c>
@@ -5667,8 +5671,8 @@
       <c r="N7" s="59"/>
     </row>
     <row r="8" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="208"/>
-      <c r="B8" s="212"/>
+      <c r="A8" s="221"/>
+      <c r="B8" s="207"/>
       <c r="C8" s="66" t="s">
         <v>263</v>
       </c>
@@ -5701,8 +5705,8 @@
       <c r="N8" s="59"/>
     </row>
     <row r="9" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="208"/>
-      <c r="B9" s="212"/>
+      <c r="A9" s="221"/>
+      <c r="B9" s="207"/>
       <c r="C9" s="66" t="s">
         <v>266</v>
       </c>
@@ -5735,8 +5739,8 @@
       <c r="N9" s="59"/>
     </row>
     <row r="10" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="208"/>
-      <c r="B10" s="212"/>
+      <c r="A10" s="221"/>
+      <c r="B10" s="207"/>
       <c r="C10" s="66" t="s">
         <v>269</v>
       </c>
@@ -5773,8 +5777,8 @@
       <c r="N10" s="59"/>
     </row>
     <row r="11" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="208"/>
-      <c r="B11" s="212"/>
+      <c r="A11" s="221"/>
+      <c r="B11" s="207"/>
       <c r="C11" s="66" t="s">
         <v>271</v>
       </c>
@@ -5811,8 +5815,8 @@
       <c r="N11" s="59"/>
     </row>
     <row r="12" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="208"/>
-      <c r="B12" s="212"/>
+      <c r="A12" s="221"/>
+      <c r="B12" s="207"/>
       <c r="C12" s="66" t="s">
         <v>275</v>
       </c>
@@ -5845,8 +5849,8 @@
       <c r="N12" s="59"/>
     </row>
     <row r="13" spans="1:14" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="208"/>
-      <c r="B13" s="212"/>
+      <c r="A13" s="221"/>
+      <c r="B13" s="207"/>
       <c r="C13" s="66" t="s">
         <v>278</v>
       </c>
@@ -5879,8 +5883,8 @@
       <c r="N13" s="59"/>
     </row>
     <row r="14" spans="1:14" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="208"/>
-      <c r="B14" s="212"/>
+      <c r="A14" s="221"/>
+      <c r="B14" s="207"/>
       <c r="C14" s="66" t="s">
         <v>279</v>
       </c>
@@ -5913,8 +5917,8 @@
       <c r="N14" s="59"/>
     </row>
     <row r="15" spans="1:14" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="208"/>
-      <c r="B15" s="212"/>
+      <c r="A15" s="221"/>
+      <c r="B15" s="207"/>
       <c r="C15" s="66" t="s">
         <v>282</v>
       </c>
@@ -5947,8 +5951,8 @@
       <c r="N15" s="59"/>
     </row>
     <row r="16" spans="1:14" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="208"/>
-      <c r="B16" s="212"/>
+      <c r="A16" s="221"/>
+      <c r="B16" s="207"/>
       <c r="C16" s="66" t="s">
         <v>285</v>
       </c>
@@ -5981,8 +5985,8 @@
       <c r="N16" s="59"/>
     </row>
     <row r="17" spans="1:128" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="208"/>
-      <c r="B17" s="212"/>
+      <c r="A17" s="221"/>
+      <c r="B17" s="207"/>
       <c r="C17" s="66" t="s">
         <v>287</v>
       </c>
@@ -6019,8 +6023,8 @@
       <c r="N17" s="59"/>
     </row>
     <row r="18" spans="1:128" ht="37.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="208"/>
-      <c r="B18" s="212"/>
+      <c r="A18" s="221"/>
+      <c r="B18" s="207"/>
       <c r="C18" s="66" t="s">
         <v>290</v>
       </c>
@@ -6057,8 +6061,8 @@
       <c r="N18" s="59"/>
     </row>
     <row r="19" spans="1:128" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="208"/>
-      <c r="B19" s="212"/>
+      <c r="A19" s="221"/>
+      <c r="B19" s="207"/>
       <c r="C19" s="66" t="s">
         <v>293</v>
       </c>
@@ -6085,8 +6089,8 @@
       <c r="N19" s="59"/>
     </row>
     <row r="20" spans="1:128" ht="31" x14ac:dyDescent="0.2">
-      <c r="A20" s="208"/>
-      <c r="B20" s="212"/>
+      <c r="A20" s="221"/>
+      <c r="B20" s="207"/>
       <c r="C20" s="66" t="s">
         <v>295</v>
       </c>
@@ -6113,8 +6117,8 @@
       <c r="N20" s="59"/>
     </row>
     <row r="21" spans="1:128" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="208"/>
-      <c r="B21" s="212"/>
+      <c r="A21" s="221"/>
+      <c r="B21" s="207"/>
       <c r="C21" s="66" t="s">
         <v>296</v>
       </c>
@@ -6141,8 +6145,8 @@
       <c r="N21" s="59"/>
     </row>
     <row r="22" spans="1:128" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="208"/>
-      <c r="B22" s="212"/>
+      <c r="A22" s="221"/>
+      <c r="B22" s="207"/>
       <c r="C22" s="66" t="s">
         <v>297</v>
       </c>
@@ -6169,8 +6173,8 @@
       <c r="N22" s="59"/>
     </row>
     <row r="23" spans="1:128" ht="31" x14ac:dyDescent="0.2">
-      <c r="A23" s="208"/>
-      <c r="B23" s="212"/>
+      <c r="A23" s="221"/>
+      <c r="B23" s="207"/>
       <c r="C23" s="66" t="s">
         <v>298</v>
       </c>
@@ -6197,8 +6201,8 @@
       <c r="N23" s="59"/>
     </row>
     <row r="24" spans="1:128" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="208"/>
-      <c r="B24" s="212"/>
+      <c r="A24" s="221"/>
+      <c r="B24" s="207"/>
       <c r="C24" s="66" t="s">
         <v>300</v>
       </c>
@@ -6225,8 +6229,8 @@
       <c r="N24" s="59"/>
     </row>
     <row r="25" spans="1:128" ht="22.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="208"/>
-      <c r="B25" s="212"/>
+      <c r="A25" s="221"/>
+      <c r="B25" s="207"/>
       <c r="C25" s="66" t="s">
         <v>301</v>
       </c>
@@ -6257,8 +6261,8 @@
       <c r="N25" s="59"/>
     </row>
     <row r="26" spans="1:128" ht="22.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="208"/>
-      <c r="B26" s="212"/>
+      <c r="A26" s="221"/>
+      <c r="B26" s="207"/>
       <c r="C26" s="66" t="s">
         <v>304</v>
       </c>
@@ -6289,7 +6293,7 @@
       <c r="N26" s="59"/>
     </row>
     <row r="27" spans="1:128" s="8" customFormat="1" ht="22.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="208"/>
+      <c r="A27" s="221"/>
       <c r="B27" s="229"/>
       <c r="C27" s="13" t="s">
         <v>305</v>
@@ -6435,8 +6439,8 @@
       <c r="DX27" s="2"/>
     </row>
     <row r="28" spans="1:128" ht="38" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="208"/>
-      <c r="B28" s="203" t="s">
+      <c r="A28" s="221"/>
+      <c r="B28" s="209" t="s">
         <v>307</v>
       </c>
       <c r="C28" s="80" t="s">
@@ -6475,8 +6479,8 @@
       <c r="N28" s="59"/>
     </row>
     <row r="29" spans="1:128" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="208"/>
-      <c r="B29" s="204"/>
+      <c r="A29" s="221"/>
+      <c r="B29" s="210"/>
       <c r="C29" s="66" t="s">
         <v>311</v>
       </c>
@@ -6513,8 +6517,8 @@
       <c r="N29" s="59"/>
     </row>
     <row r="30" spans="1:128" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="208"/>
-      <c r="B30" s="204"/>
+      <c r="A30" s="221"/>
+      <c r="B30" s="210"/>
       <c r="C30" s="66" t="s">
         <v>312</v>
       </c>
@@ -6551,8 +6555,8 @@
       <c r="N30" s="59"/>
     </row>
     <row r="31" spans="1:128" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="208"/>
-      <c r="B31" s="204"/>
+      <c r="A31" s="221"/>
+      <c r="B31" s="210"/>
       <c r="C31" s="66" t="s">
         <v>313</v>
       </c>
@@ -6589,8 +6593,8 @@
       <c r="N31" s="59"/>
     </row>
     <row r="32" spans="1:128" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="208"/>
-      <c r="B32" s="204"/>
+      <c r="A32" s="221"/>
+      <c r="B32" s="210"/>
       <c r="C32" s="66" t="s">
         <v>316</v>
       </c>
@@ -6627,8 +6631,8 @@
       <c r="N32" s="59"/>
     </row>
     <row r="33" spans="1:128" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="208"/>
-      <c r="B33" s="204"/>
+      <c r="A33" s="221"/>
+      <c r="B33" s="210"/>
       <c r="C33" s="66" t="s">
         <v>318</v>
       </c>
@@ -6665,8 +6669,8 @@
       <c r="N33" s="59"/>
     </row>
     <row r="34" spans="1:128" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="208"/>
-      <c r="B34" s="204"/>
+      <c r="A34" s="221"/>
+      <c r="B34" s="210"/>
       <c r="C34" s="66" t="s">
         <v>320</v>
       </c>
@@ -6701,8 +6705,8 @@
       <c r="N34" s="59"/>
     </row>
     <row r="35" spans="1:128" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="208"/>
-      <c r="B35" s="204"/>
+      <c r="A35" s="221"/>
+      <c r="B35" s="210"/>
       <c r="C35" s="66" t="s">
         <v>321</v>
       </c>
@@ -6737,8 +6741,8 @@
       <c r="N35" s="59"/>
     </row>
     <row r="36" spans="1:128" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="208"/>
-      <c r="B36" s="204"/>
+      <c r="A36" s="221"/>
+      <c r="B36" s="210"/>
       <c r="C36" s="66" t="s">
         <v>322</v>
       </c>
@@ -6773,8 +6777,8 @@
       <c r="N36" s="59"/>
     </row>
     <row r="37" spans="1:128" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="208"/>
-      <c r="B37" s="204"/>
+      <c r="A37" s="221"/>
+      <c r="B37" s="210"/>
       <c r="C37" s="66" t="s">
         <v>323</v>
       </c>
@@ -6809,8 +6813,8 @@
       <c r="N37" s="59"/>
     </row>
     <row r="38" spans="1:128" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="208"/>
-      <c r="B38" s="204"/>
+      <c r="A38" s="221"/>
+      <c r="B38" s="210"/>
       <c r="C38" s="66" t="s">
         <v>324</v>
       </c>
@@ -6835,8 +6839,8 @@
       <c r="N38" s="59"/>
     </row>
     <row r="39" spans="1:128" ht="31" x14ac:dyDescent="0.2">
-      <c r="A39" s="208"/>
-      <c r="B39" s="204"/>
+      <c r="A39" s="221"/>
+      <c r="B39" s="210"/>
       <c r="C39" s="66" t="s">
         <v>325</v>
       </c>
@@ -6861,8 +6865,8 @@
       <c r="N39" s="59"/>
     </row>
     <row r="40" spans="1:128" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="208"/>
-      <c r="B40" s="210"/>
+      <c r="A40" s="221"/>
+      <c r="B40" s="211"/>
       <c r="C40" s="152" t="s">
         <v>326</v>
       </c>
@@ -6888,7 +6892,7 @@
     </row>
     <row r="41" spans="1:128" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="228"/>
-      <c r="B41" s="203" t="s">
+      <c r="B41" s="209" t="s">
         <v>327</v>
       </c>
       <c r="C41" s="80" t="s">
@@ -6920,7 +6924,7 @@
     </row>
     <row r="42" spans="1:128" ht="31" x14ac:dyDescent="0.2">
       <c r="A42" s="228"/>
-      <c r="B42" s="204"/>
+      <c r="B42" s="210"/>
       <c r="C42" s="66" t="s">
         <v>331</v>
       </c>
@@ -6948,7 +6952,7 @@
     </row>
     <row r="43" spans="1:128" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="228"/>
-      <c r="B43" s="204"/>
+      <c r="B43" s="210"/>
       <c r="C43" s="66" t="s">
         <v>332</v>
       </c>
@@ -6986,7 +6990,7 @@
     </row>
     <row r="44" spans="1:128" ht="31" x14ac:dyDescent="0.2">
       <c r="A44" s="228"/>
-      <c r="B44" s="204"/>
+      <c r="B44" s="210"/>
       <c r="C44" s="66" t="s">
         <v>335</v>
       </c>
@@ -7014,7 +7018,7 @@
     </row>
     <row r="45" spans="1:128" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="228"/>
-      <c r="B45" s="204"/>
+      <c r="B45" s="210"/>
       <c r="C45" s="66" t="s">
         <v>336</v>
       </c>
@@ -7052,7 +7056,7 @@
     </row>
     <row r="46" spans="1:128" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="228"/>
-      <c r="B46" s="204"/>
+      <c r="B46" s="210"/>
       <c r="C46" s="66" t="s">
         <v>337</v>
       </c>
@@ -7088,7 +7092,7 @@
     </row>
     <row r="47" spans="1:128" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="228"/>
-      <c r="B47" s="204"/>
+      <c r="B47" s="210"/>
       <c r="C47" s="66" t="s">
         <v>338</v>
       </c>
@@ -7114,7 +7118,7 @@
     </row>
     <row r="48" spans="1:128" s="8" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="228"/>
-      <c r="B48" s="204"/>
+      <c r="B48" s="210"/>
       <c r="C48" s="66" t="s">
         <v>339</v>
       </c>
@@ -7254,7 +7258,7 @@
     </row>
     <row r="49" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="228"/>
-      <c r="B49" s="204"/>
+      <c r="B49" s="210"/>
       <c r="C49" s="66" t="s">
         <v>340</v>
       </c>
@@ -7286,7 +7290,7 @@
     </row>
     <row r="50" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="228"/>
-      <c r="B50" s="204"/>
+      <c r="B50" s="210"/>
       <c r="C50" s="66" t="s">
         <v>342</v>
       </c>
@@ -7312,7 +7316,7 @@
     </row>
     <row r="51" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="228"/>
-      <c r="B51" s="204"/>
+      <c r="B51" s="210"/>
       <c r="C51" s="66" t="s">
         <v>343</v>
       </c>
@@ -7338,7 +7342,7 @@
     </row>
     <row r="52" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="228"/>
-      <c r="B52" s="204"/>
+      <c r="B52" s="210"/>
       <c r="C52" s="66" t="s">
         <v>344</v>
       </c>
@@ -7364,7 +7368,7 @@
     </row>
     <row r="53" spans="1:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="228"/>
-      <c r="B53" s="205"/>
+      <c r="B53" s="218"/>
       <c r="C53" s="93" t="s">
         <v>345</v>
       </c>
@@ -7389,7 +7393,7 @@
       <c r="N53" s="59"/>
     </row>
     <row r="54" spans="1:14" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="209"/>
+      <c r="A54" s="222"/>
       <c r="B54" s="175" t="s">
         <v>346</v>
       </c>
@@ -11782,12 +11786,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="M2:M4"/>
     <mergeCell ref="A5:A54"/>
     <mergeCell ref="B28:B40"/>
     <mergeCell ref="B41:B53"/>
@@ -11796,6 +11794,12 @@
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="B6:B27"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="M2:M4"/>
   </mergeCells>
   <phoneticPr fontId="27" type="noConversion"/>
   <conditionalFormatting sqref="D2:G54">
@@ -11921,8 +11925,8 @@
       <c r="M1" s="202"/>
     </row>
     <row r="2" spans="1:13" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="244"/>
-      <c r="B2" s="246"/>
+      <c r="A2" s="248"/>
+      <c r="B2" s="250"/>
       <c r="C2" s="223"/>
       <c r="D2" s="69" t="s">
         <v>57</v>
@@ -11936,28 +11940,28 @@
       <c r="G2" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="250" t="s">
+      <c r="H2" s="254" t="s">
         <v>350</v>
       </c>
-      <c r="I2" s="253" t="s">
+      <c r="I2" s="240" t="s">
         <v>88</v>
       </c>
-      <c r="J2" s="253" t="s">
+      <c r="J2" s="240" t="s">
         <v>89</v>
       </c>
-      <c r="K2" s="253" t="s">
+      <c r="K2" s="240" t="s">
         <v>90</v>
       </c>
-      <c r="L2" s="253" t="s">
+      <c r="L2" s="240" t="s">
         <v>91</v>
       </c>
-      <c r="M2" s="256" t="s">
+      <c r="M2" s="243" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="245"/>
-      <c r="B3" s="247"/>
+      <c r="A3" s="249"/>
+      <c r="B3" s="251"/>
       <c r="C3" s="224"/>
       <c r="D3" s="16" t="str">
         <f>'Scenario overview'!B6</f>
@@ -11975,17 +11979,17 @@
         <f>'Scenario overview'!B9</f>
         <v>A low-burden country achieving one or more of the 95s</v>
       </c>
-      <c r="H3" s="251"/>
-      <c r="I3" s="254"/>
-      <c r="J3" s="254"/>
-      <c r="K3" s="254"/>
-      <c r="L3" s="254"/>
-      <c r="M3" s="257"/>
+      <c r="H3" s="255"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
+      <c r="L3" s="241"/>
+      <c r="M3" s="244"/>
     </row>
     <row r="4" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="245"/>
-      <c r="B4" s="248"/>
-      <c r="C4" s="249"/>
+      <c r="A4" s="249"/>
+      <c r="B4" s="252"/>
+      <c r="C4" s="253"/>
       <c r="D4" s="31" t="str">
         <f>'Scenario overview'!C6</f>
         <v>Limited, possibly some unsuppressed ART clients and some specific sub-segments that are generally underserved</v>
@@ -12002,18 +12006,18 @@
         <f>'Scenario overview'!C9</f>
         <v>Clinically unstable/symptomatic, gaps in all population groups</v>
       </c>
-      <c r="H4" s="252"/>
-      <c r="I4" s="255"/>
-      <c r="J4" s="255"/>
-      <c r="K4" s="255"/>
-      <c r="L4" s="255"/>
-      <c r="M4" s="258"/>
+      <c r="H4" s="256"/>
+      <c r="I4" s="242"/>
+      <c r="J4" s="242"/>
+      <c r="K4" s="242"/>
+      <c r="L4" s="242"/>
+      <c r="M4" s="245"/>
     </row>
     <row r="5" spans="1:13" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="240" t="s">
+      <c r="A5" s="257" t="s">
         <v>351</v>
       </c>
-      <c r="B5" s="203" t="s">
+      <c r="B5" s="209" t="s">
         <v>352</v>
       </c>
       <c r="C5" s="80" t="s">
@@ -12051,8 +12055,8 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="240"/>
-      <c r="B6" s="204"/>
+      <c r="A6" s="257"/>
+      <c r="B6" s="210"/>
       <c r="C6" s="66" t="s">
         <v>356</v>
       </c>
@@ -12088,8 +12092,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="240"/>
-      <c r="B7" s="205"/>
+      <c r="A7" s="257"/>
+      <c r="B7" s="218"/>
       <c r="C7" s="9" t="s">
         <v>357</v>
       </c>
@@ -12125,8 +12129,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="240"/>
-      <c r="B8" s="203" t="s">
+      <c r="A8" s="257"/>
+      <c r="B8" s="209" t="s">
         <v>359</v>
       </c>
       <c r="C8" s="80" t="s">
@@ -12164,8 +12168,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="240"/>
-      <c r="B9" s="205"/>
+      <c r="A9" s="257"/>
+      <c r="B9" s="218"/>
       <c r="C9" s="9" t="s">
         <v>363</v>
       </c>
@@ -12201,8 +12205,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="240"/>
-      <c r="B10" s="203" t="s">
+      <c r="A10" s="257"/>
+      <c r="B10" s="209" t="s">
         <v>366</v>
       </c>
       <c r="C10" s="80" t="s">
@@ -12240,8 +12244,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="31.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="240"/>
-      <c r="B11" s="204"/>
+      <c r="A11" s="257"/>
+      <c r="B11" s="210"/>
       <c r="C11" s="66" t="s">
         <v>370</v>
       </c>
@@ -12269,8 +12273,8 @@
       <c r="M11" s="71"/>
     </row>
     <row r="12" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="240"/>
-      <c r="B12" s="205"/>
+      <c r="A12" s="257"/>
+      <c r="B12" s="218"/>
       <c r="C12" s="9" t="s">
         <v>373</v>
       </c>
@@ -12298,8 +12302,8 @@
       <c r="M12" s="124"/>
     </row>
     <row r="13" spans="1:13" ht="46.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="240"/>
-      <c r="B13" s="203" t="s">
+      <c r="A13" s="257"/>
+      <c r="B13" s="209" t="s">
         <v>375</v>
       </c>
       <c r="C13" s="80" t="s">
@@ -12335,8 +12339,8 @@
       <c r="M13" s="118"/>
     </row>
     <row r="14" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="240"/>
-      <c r="B14" s="204"/>
+      <c r="A14" s="257"/>
+      <c r="B14" s="210"/>
       <c r="C14" s="66" t="s">
         <v>380</v>
       </c>
@@ -12372,8 +12376,8 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="240"/>
-      <c r="B15" s="204"/>
+      <c r="A15" s="257"/>
+      <c r="B15" s="210"/>
       <c r="C15" s="66" t="s">
         <v>382</v>
       </c>
@@ -12409,8 +12413,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="31.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="240"/>
-      <c r="B16" s="204"/>
+      <c r="A16" s="257"/>
+      <c r="B16" s="210"/>
       <c r="C16" s="66" t="s">
         <v>383</v>
       </c>
@@ -12440,8 +12444,8 @@
       <c r="M16" s="104"/>
     </row>
     <row r="17" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A17" s="240"/>
-      <c r="B17" s="204"/>
+      <c r="A17" s="257"/>
+      <c r="B17" s="210"/>
       <c r="C17" s="66" t="s">
         <v>386</v>
       </c>
@@ -12471,8 +12475,8 @@
       <c r="M17" s="104"/>
     </row>
     <row r="18" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="240"/>
-      <c r="B18" s="204"/>
+      <c r="A18" s="257"/>
+      <c r="B18" s="210"/>
       <c r="C18" s="98" t="s">
         <v>388</v>
       </c>
@@ -12502,8 +12506,8 @@
       <c r="M18" s="104"/>
     </row>
     <row r="19" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="240"/>
-      <c r="B19" s="204"/>
+      <c r="A19" s="257"/>
+      <c r="B19" s="210"/>
       <c r="C19" s="66" t="s">
         <v>389</v>
       </c>
@@ -12533,8 +12537,8 @@
       <c r="M19" s="104"/>
     </row>
     <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="240"/>
-      <c r="B20" s="204"/>
+      <c r="A20" s="257"/>
+      <c r="B20" s="210"/>
       <c r="C20" s="66" t="s">
         <v>391</v>
       </c>
@@ -12564,8 +12568,8 @@
       <c r="M20" s="104"/>
     </row>
     <row r="21" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="240"/>
-      <c r="B21" s="204"/>
+      <c r="A21" s="257"/>
+      <c r="B21" s="210"/>
       <c r="C21" s="66" t="s">
         <v>392</v>
       </c>
@@ -12595,8 +12599,8 @@
       <c r="M21" s="104"/>
     </row>
     <row r="22" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="240"/>
-      <c r="B22" s="204"/>
+      <c r="A22" s="257"/>
+      <c r="B22" s="210"/>
       <c r="C22" s="66" t="s">
         <v>393</v>
       </c>
@@ -12630,8 +12634,8 @@
       <c r="M22" s="104"/>
     </row>
     <row r="23" spans="1:13" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="240"/>
-      <c r="B23" s="205"/>
+      <c r="A23" s="257"/>
+      <c r="B23" s="218"/>
       <c r="C23" s="9" t="s">
         <v>394</v>
       </c>
@@ -12667,8 +12671,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="240"/>
-      <c r="B24" s="203" t="s">
+      <c r="A24" s="257"/>
+      <c r="B24" s="209" t="s">
         <v>397</v>
       </c>
       <c r="C24" s="80" t="s">
@@ -12704,8 +12708,8 @@
       <c r="M24" s="118"/>
     </row>
     <row r="25" spans="1:13" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="240"/>
-      <c r="B25" s="204"/>
+      <c r="A25" s="257"/>
+      <c r="B25" s="210"/>
       <c r="C25" s="66" t="s">
         <v>399</v>
       </c>
@@ -12739,8 +12743,8 @@
       <c r="M25" s="104"/>
     </row>
     <row r="26" spans="1:13" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="240"/>
-      <c r="B26" s="204"/>
+      <c r="A26" s="257"/>
+      <c r="B26" s="210"/>
       <c r="C26" s="66" t="s">
         <v>400</v>
       </c>
@@ -12774,8 +12778,8 @@
       <c r="M26" s="104"/>
     </row>
     <row r="27" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="240"/>
-      <c r="B27" s="204"/>
+      <c r="A27" s="257"/>
+      <c r="B27" s="210"/>
       <c r="C27" s="66" t="s">
         <v>402</v>
       </c>
@@ -12809,8 +12813,8 @@
       <c r="M27" s="104"/>
     </row>
     <row r="28" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="240"/>
-      <c r="B28" s="204"/>
+      <c r="A28" s="257"/>
+      <c r="B28" s="210"/>
       <c r="C28" s="66" t="s">
         <v>403</v>
       </c>
@@ -12844,8 +12848,8 @@
       <c r="M28" s="104"/>
     </row>
     <row r="29" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="240"/>
-      <c r="B29" s="204"/>
+      <c r="A29" s="257"/>
+      <c r="B29" s="210"/>
       <c r="C29" s="66" t="s">
         <v>405</v>
       </c>
@@ -12873,8 +12877,8 @@
       <c r="M29" s="104"/>
     </row>
     <row r="30" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="240"/>
-      <c r="B30" s="204"/>
+      <c r="A30" s="257"/>
+      <c r="B30" s="210"/>
       <c r="C30" s="66" t="s">
         <v>407</v>
       </c>
@@ -12902,8 +12906,8 @@
       <c r="M30" s="104"/>
     </row>
     <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="240"/>
-      <c r="B31" s="204"/>
+      <c r="A31" s="257"/>
+      <c r="B31" s="210"/>
       <c r="C31" s="66" t="s">
         <v>393</v>
       </c>
@@ -12939,8 +12943,8 @@
       </c>
     </row>
     <row r="32" spans="1:13" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="240"/>
-      <c r="B32" s="204"/>
+      <c r="A32" s="257"/>
+      <c r="B32" s="210"/>
       <c r="C32" s="66" t="s">
         <v>410</v>
       </c>
@@ -12974,8 +12978,8 @@
       <c r="M32" s="104"/>
     </row>
     <row r="33" spans="1:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="240"/>
-      <c r="B33" s="205"/>
+      <c r="A33" s="257"/>
+      <c r="B33" s="218"/>
       <c r="C33" s="9" t="s">
         <v>412</v>
       </c>
@@ -13003,8 +13007,8 @@
       <c r="M33" s="117"/>
     </row>
     <row r="34" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="240"/>
-      <c r="B34" s="203" t="s">
+      <c r="A34" s="257"/>
+      <c r="B34" s="209" t="s">
         <v>415</v>
       </c>
       <c r="C34" s="127" t="s">
@@ -13040,8 +13044,8 @@
       </c>
     </row>
     <row r="35" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="240"/>
-      <c r="B35" s="204"/>
+      <c r="A35" s="257"/>
+      <c r="B35" s="210"/>
       <c r="C35" s="122" t="s">
         <v>418</v>
       </c>
@@ -13075,8 +13079,8 @@
       </c>
     </row>
     <row r="36" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="240"/>
-      <c r="B36" s="204"/>
+      <c r="A36" s="257"/>
+      <c r="B36" s="210"/>
       <c r="C36" s="66" t="s">
         <v>419</v>
       </c>
@@ -13110,8 +13114,8 @@
       </c>
     </row>
     <row r="37" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="240"/>
-      <c r="B37" s="205"/>
+      <c r="A37" s="257"/>
+      <c r="B37" s="218"/>
       <c r="C37" s="9" t="s">
         <v>421</v>
       </c>
@@ -13145,7 +13149,7 @@
       </c>
     </row>
     <row r="38" spans="1:13" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="241"/>
+      <c r="A38" s="258"/>
       <c r="B38" s="73" t="s">
         <v>422</v>
       </c>
@@ -13191,6 +13195,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A5:A38"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B13:B23"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B5:B7"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
@@ -13201,13 +13212,6 @@
     <mergeCell ref="K2:K4"/>
     <mergeCell ref="L2:L4"/>
     <mergeCell ref="M2:M4"/>
-    <mergeCell ref="A5:A38"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B13:B23"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:G38">
     <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
@@ -13756,35 +13760,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="214" t="s">
+      <c r="A1" s="203" t="s">
         <v>432</v>
       </c>
-      <c r="B1" s="215"/>
-      <c r="C1" s="215"/>
-      <c r="D1" s="215"/>
-      <c r="E1" s="215"/>
-      <c r="F1" s="215"/>
-      <c r="G1" s="215"/>
-      <c r="H1" s="215"/>
-      <c r="I1" s="215"/>
-      <c r="J1" s="215"/>
-      <c r="K1" s="215"/>
-      <c r="L1" s="216"/>
+      <c r="B1" s="204"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="204"/>
+      <c r="K1" s="204"/>
+      <c r="L1" s="205"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="217" t="s">
+      <c r="A2" s="212" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="219" t="s">
+      <c r="B2" s="214" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="219" t="s">
+      <c r="C2" s="214" t="s">
         <v>85</v>
       </c>
       <c r="D2" s="16"/>
       <c r="E2" s="16"/>
       <c r="F2" s="16"/>
-      <c r="G2" s="221" t="s">
+      <c r="G2" s="216" t="s">
         <v>86</v>
       </c>
       <c r="H2" s="95"/>
@@ -13794,9 +13798,9 @@
       <c r="L2" s="102"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="217"/>
-      <c r="B3" s="219"/>
-      <c r="C3" s="219"/>
+      <c r="A3" s="212"/>
+      <c r="B3" s="214"/>
+      <c r="C3" s="214"/>
       <c r="D3" s="16" t="str">
         <f>'Scenario overview'!B18</f>
         <v>SCENARIO 1</v>
@@ -13806,7 +13810,7 @@
         <v>COUNTRY NAME</v>
       </c>
       <c r="F3" s="16"/>
-      <c r="G3" s="221"/>
+      <c r="G3" s="216"/>
       <c r="H3" s="95"/>
       <c r="I3" s="95"/>
       <c r="J3" s="95"/>
@@ -13814,15 +13818,15 @@
       <c r="L3" s="102"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="218"/>
-      <c r="B4" s="220"/>
-      <c r="C4" s="220"/>
+      <c r="A4" s="213"/>
+      <c r="B4" s="215"/>
+      <c r="C4" s="215"/>
       <c r="D4" s="31"/>
       <c r="E4" s="31"/>
       <c r="F4" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="G4" s="222"/>
+      <c r="G4" s="217"/>
       <c r="H4" s="108" t="s">
         <v>88</v>
       </c>
@@ -13840,10 +13844,10 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="207" t="s">
+      <c r="A5" s="220" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="211" t="s">
+      <c r="B5" s="206" t="s">
         <v>94</v>
       </c>
       <c r="C5" s="110" t="s">
@@ -13875,8 +13879,8 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="208"/>
-      <c r="B6" s="212"/>
+      <c r="A6" s="221"/>
+      <c r="B6" s="207"/>
       <c r="C6" s="96" t="s">
         <v>101</v>
       </c>
@@ -13906,8 +13910,8 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="208"/>
-      <c r="B7" s="212"/>
+      <c r="A7" s="221"/>
+      <c r="B7" s="207"/>
       <c r="C7" s="96" t="s">
         <v>105</v>
       </c>
@@ -13937,8 +13941,8 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="208"/>
-      <c r="B8" s="212"/>
+      <c r="A8" s="221"/>
+      <c r="B8" s="207"/>
       <c r="C8" s="96" t="s">
         <v>435</v>
       </c>
@@ -13964,8 +13968,8 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="208"/>
-      <c r="B9" s="212"/>
+      <c r="A9" s="221"/>
+      <c r="B9" s="207"/>
       <c r="C9" s="98" t="s">
         <v>113</v>
       </c>
@@ -13991,8 +13995,8 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="208"/>
-      <c r="B10" s="212"/>
+      <c r="A10" s="221"/>
+      <c r="B10" s="207"/>
       <c r="C10" s="98" t="s">
         <v>114</v>
       </c>
@@ -14018,8 +14022,8 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="208"/>
-      <c r="B11" s="212"/>
+      <c r="A11" s="221"/>
+      <c r="B11" s="207"/>
       <c r="C11" s="98" t="s">
         <v>115</v>
       </c>
@@ -14045,8 +14049,8 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="208"/>
-      <c r="B12" s="212"/>
+      <c r="A12" s="221"/>
+      <c r="B12" s="207"/>
       <c r="C12" s="98" t="s">
         <v>116</v>
       </c>
@@ -14076,8 +14080,8 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="208"/>
-      <c r="B13" s="212"/>
+      <c r="A13" s="221"/>
+      <c r="B13" s="207"/>
       <c r="C13" s="98" t="s">
         <v>436</v>
       </c>
@@ -14103,8 +14107,8 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="208"/>
-      <c r="B14" s="212"/>
+      <c r="A14" s="221"/>
+      <c r="B14" s="207"/>
       <c r="C14" s="98" t="s">
         <v>119</v>
       </c>
@@ -14134,8 +14138,8 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="61" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="208"/>
-      <c r="B15" s="213"/>
+      <c r="A15" s="221"/>
+      <c r="B15" s="208"/>
       <c r="C15" s="157" t="s">
         <v>120</v>
       </c>
@@ -14157,8 +14161,8 @@
       <c r="L15" s="115"/>
     </row>
     <row r="16" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="208"/>
-      <c r="B16" s="203" t="s">
+      <c r="A16" s="221"/>
+      <c r="B16" s="209" t="s">
         <v>123</v>
       </c>
       <c r="C16" s="110" t="s">
@@ -14190,8 +14194,8 @@
       </c>
     </row>
     <row r="17" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="208"/>
-      <c r="B17" s="204"/>
+      <c r="A17" s="221"/>
+      <c r="B17" s="210"/>
       <c r="C17" s="96" t="s">
         <v>437</v>
       </c>
@@ -14221,8 +14225,8 @@
       </c>
     </row>
     <row r="18" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="208"/>
-      <c r="B18" s="204"/>
+      <c r="A18" s="221"/>
+      <c r="B18" s="210"/>
       <c r="C18" s="96" t="s">
         <v>132</v>
       </c>
@@ -14252,8 +14256,8 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="208"/>
-      <c r="B19" s="204"/>
+      <c r="A19" s="221"/>
+      <c r="B19" s="210"/>
       <c r="C19" s="96" t="s">
         <v>135</v>
       </c>
@@ -14283,8 +14287,8 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="208"/>
-      <c r="B20" s="204"/>
+      <c r="A20" s="221"/>
+      <c r="B20" s="210"/>
       <c r="C20" s="96" t="s">
         <v>139</v>
       </c>
@@ -14314,8 +14318,8 @@
       </c>
     </row>
     <row r="21" spans="1:12" ht="34.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="208"/>
-      <c r="B21" s="210"/>
+      <c r="A21" s="221"/>
+      <c r="B21" s="211"/>
       <c r="C21" s="157" t="s">
         <v>142</v>
       </c>
@@ -14345,8 +14349,8 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="208"/>
-      <c r="B22" s="203" t="s">
+      <c r="A22" s="221"/>
+      <c r="B22" s="209" t="s">
         <v>146</v>
       </c>
       <c r="C22" s="110" t="s">
@@ -14378,8 +14382,8 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="208"/>
-      <c r="B23" s="204"/>
+      <c r="A23" s="221"/>
+      <c r="B23" s="210"/>
       <c r="C23" s="96" t="s">
         <v>149</v>
       </c>
@@ -14409,8 +14413,8 @@
       </c>
     </row>
     <row r="24" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="208"/>
-      <c r="B24" s="204"/>
+      <c r="A24" s="221"/>
+      <c r="B24" s="210"/>
       <c r="C24" s="96" t="s">
         <v>150</v>
       </c>
@@ -14440,8 +14444,8 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="208"/>
-      <c r="B25" s="204"/>
+      <c r="A25" s="221"/>
+      <c r="B25" s="210"/>
       <c r="C25" s="96" t="s">
         <v>151</v>
       </c>
@@ -14471,8 +14475,8 @@
       </c>
     </row>
     <row r="26" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="208"/>
-      <c r="B26" s="204"/>
+      <c r="A26" s="221"/>
+      <c r="B26" s="210"/>
       <c r="C26" s="96" t="s">
         <v>152</v>
       </c>
@@ -14502,8 +14506,8 @@
       </c>
     </row>
     <row r="27" spans="1:12" ht="34.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="208"/>
-      <c r="B27" s="210"/>
+      <c r="A27" s="221"/>
+      <c r="B27" s="211"/>
       <c r="C27" s="157" t="s">
         <v>438</v>
       </c>
@@ -14533,8 +14537,8 @@
       </c>
     </row>
     <row r="28" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="208"/>
-      <c r="B28" s="203" t="s">
+      <c r="A28" s="221"/>
+      <c r="B28" s="209" t="s">
         <v>155</v>
       </c>
       <c r="C28" s="80" t="s">
@@ -14566,8 +14570,8 @@
       </c>
     </row>
     <row r="29" spans="1:12" ht="31" x14ac:dyDescent="0.2">
-      <c r="A29" s="208"/>
-      <c r="B29" s="204"/>
+      <c r="A29" s="221"/>
+      <c r="B29" s="210"/>
       <c r="C29" s="66" t="s">
         <v>158</v>
       </c>
@@ -14587,8 +14591,8 @@
       <c r="L29" s="104"/>
     </row>
     <row r="30" spans="1:12" ht="31.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="208"/>
-      <c r="B30" s="204"/>
+      <c r="A30" s="221"/>
+      <c r="B30" s="210"/>
       <c r="C30" s="66" t="s">
         <v>159</v>
       </c>
@@ -14608,8 +14612,8 @@
       <c r="L30" s="104"/>
     </row>
     <row r="31" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="208"/>
-      <c r="B31" s="204"/>
+      <c r="A31" s="221"/>
+      <c r="B31" s="210"/>
       <c r="C31" s="66" t="s">
         <v>161</v>
       </c>
@@ -14629,8 +14633,8 @@
       <c r="L31" s="104"/>
     </row>
     <row r="32" spans="1:12" ht="31.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="208"/>
-      <c r="B32" s="204"/>
+      <c r="A32" s="221"/>
+      <c r="B32" s="210"/>
       <c r="C32" s="66" t="s">
         <v>162</v>
       </c>
@@ -14656,8 +14660,8 @@
       </c>
     </row>
     <row r="33" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="208"/>
-      <c r="B33" s="204"/>
+      <c r="A33" s="221"/>
+      <c r="B33" s="210"/>
       <c r="C33" s="66" t="s">
         <v>164</v>
       </c>
@@ -14683,8 +14687,8 @@
       </c>
     </row>
     <row r="34" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="208"/>
-      <c r="B34" s="204"/>
+      <c r="A34" s="221"/>
+      <c r="B34" s="210"/>
       <c r="C34" s="66" t="s">
         <v>165</v>
       </c>
@@ -14710,8 +14714,8 @@
       </c>
     </row>
     <row r="35" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="208"/>
-      <c r="B35" s="204"/>
+      <c r="A35" s="221"/>
+      <c r="B35" s="210"/>
       <c r="C35" s="66" t="s">
         <v>167</v>
       </c>
@@ -14731,8 +14735,8 @@
       <c r="L35" s="104"/>
     </row>
     <row r="36" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="208"/>
-      <c r="B36" s="204"/>
+      <c r="A36" s="221"/>
+      <c r="B36" s="210"/>
       <c r="C36" s="96" t="s">
         <v>168</v>
       </c>
@@ -14762,8 +14766,8 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="208"/>
-      <c r="B37" s="204"/>
+      <c r="A37" s="221"/>
+      <c r="B37" s="210"/>
       <c r="C37" s="98" t="s">
         <v>173</v>
       </c>
@@ -14783,8 +14787,8 @@
       <c r="L37" s="104"/>
     </row>
     <row r="38" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="208"/>
-      <c r="B38" s="210"/>
+      <c r="A38" s="221"/>
+      <c r="B38" s="211"/>
       <c r="C38" s="167" t="s">
         <v>174</v>
       </c>
@@ -14802,8 +14806,8 @@
       <c r="L38" s="117"/>
     </row>
     <row r="39" spans="1:12" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="208"/>
-      <c r="B39" s="211" t="s">
+      <c r="A39" s="221"/>
+      <c r="B39" s="206" t="s">
         <v>175</v>
       </c>
       <c r="C39" s="80" t="s">
@@ -14835,8 +14839,8 @@
       </c>
     </row>
     <row r="40" spans="1:12" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="208"/>
-      <c r="B40" s="212"/>
+      <c r="A40" s="221"/>
+      <c r="B40" s="207"/>
       <c r="C40" s="66" t="s">
         <v>180</v>
       </c>
@@ -14860,8 +14864,8 @@
       </c>
     </row>
     <row r="41" spans="1:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="208"/>
-      <c r="B41" s="212"/>
+      <c r="A41" s="221"/>
+      <c r="B41" s="207"/>
       <c r="C41" s="66" t="s">
         <v>182</v>
       </c>
@@ -14891,8 +14895,8 @@
       </c>
     </row>
     <row r="42" spans="1:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="208"/>
-      <c r="B42" s="212"/>
+      <c r="A42" s="221"/>
+      <c r="B42" s="207"/>
       <c r="C42" s="66" t="s">
         <v>186</v>
       </c>
@@ -14922,8 +14926,8 @@
       </c>
     </row>
     <row r="43" spans="1:12" ht="31.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="208"/>
-      <c r="B43" s="213"/>
+      <c r="A43" s="221"/>
+      <c r="B43" s="208"/>
       <c r="C43" s="152" t="s">
         <v>191</v>
       </c>
@@ -14953,8 +14957,8 @@
       </c>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="208"/>
-      <c r="B44" s="211" t="s">
+      <c r="A44" s="221"/>
+      <c r="B44" s="206" t="s">
         <v>194</v>
       </c>
       <c r="C44" s="110" t="s">
@@ -14980,8 +14984,8 @@
       <c r="L44" s="118"/>
     </row>
     <row r="45" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="208"/>
-      <c r="B45" s="212"/>
+      <c r="A45" s="221"/>
+      <c r="B45" s="207"/>
       <c r="C45" s="96" t="s">
         <v>199</v>
       </c>
@@ -15011,8 +15015,8 @@
       </c>
     </row>
     <row r="46" spans="1:12" ht="34.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="208"/>
-      <c r="B46" s="212"/>
+      <c r="A46" s="221"/>
+      <c r="B46" s="207"/>
       <c r="C46" s="96" t="s">
         <v>203</v>
       </c>
@@ -15036,8 +15040,8 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="34.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="208"/>
-      <c r="B47" s="212"/>
+      <c r="A47" s="221"/>
+      <c r="B47" s="207"/>
       <c r="C47" s="96" t="s">
         <v>205</v>
       </c>
@@ -15061,8 +15065,8 @@
       </c>
     </row>
     <row r="48" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="208"/>
-      <c r="B48" s="212"/>
+      <c r="A48" s="221"/>
+      <c r="B48" s="207"/>
       <c r="C48" s="100" t="s">
         <v>206</v>
       </c>
@@ -15086,8 +15090,8 @@
       <c r="L48" s="104"/>
     </row>
     <row r="49" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="208"/>
-      <c r="B49" s="212"/>
+      <c r="A49" s="221"/>
+      <c r="B49" s="207"/>
       <c r="C49" s="96" t="s">
         <v>207</v>
       </c>
@@ -15117,8 +15121,8 @@
       </c>
     </row>
     <row r="50" spans="1:12" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="208"/>
-      <c r="B50" s="213"/>
+      <c r="A50" s="221"/>
+      <c r="B50" s="208"/>
       <c r="C50" s="157" t="s">
         <v>208</v>
       </c>
@@ -15148,8 +15152,8 @@
       </c>
     </row>
     <row r="51" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="208"/>
-      <c r="B51" s="203" t="s">
+      <c r="A51" s="221"/>
+      <c r="B51" s="209" t="s">
         <v>210</v>
       </c>
       <c r="C51" s="110" t="s">
@@ -15173,8 +15177,8 @@
       <c r="L51" s="118"/>
     </row>
     <row r="52" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="208"/>
-      <c r="B52" s="204"/>
+      <c r="A52" s="221"/>
+      <c r="B52" s="210"/>
       <c r="C52" s="96" t="s">
         <v>213</v>
       </c>
@@ -15200,8 +15204,8 @@
       <c r="L52" s="104"/>
     </row>
     <row r="53" spans="1:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="208"/>
-      <c r="B53" s="204"/>
+      <c r="A53" s="221"/>
+      <c r="B53" s="210"/>
       <c r="C53" s="66" t="s">
         <v>216</v>
       </c>
@@ -15211,7 +15215,7 @@
       </c>
       <c r="E53" s="33"/>
       <c r="F53" s="33"/>
-      <c r="G53" s="206" t="s">
+      <c r="G53" s="219" t="s">
         <v>217</v>
       </c>
       <c r="H53" s="60" t="s">
@@ -15231,8 +15235,8 @@
       </c>
     </row>
     <row r="54" spans="1:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="208"/>
-      <c r="B54" s="204"/>
+      <c r="A54" s="221"/>
+      <c r="B54" s="210"/>
       <c r="C54" s="66" t="s">
         <v>218</v>
       </c>
@@ -15242,7 +15246,7 @@
       </c>
       <c r="E54" s="33"/>
       <c r="F54" s="33"/>
-      <c r="G54" s="206"/>
+      <c r="G54" s="219"/>
       <c r="H54" s="60" t="s">
         <v>483</v>
       </c>
@@ -15260,8 +15264,8 @@
       </c>
     </row>
     <row r="55" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="208"/>
-      <c r="B55" s="204"/>
+      <c r="A55" s="221"/>
+      <c r="B55" s="210"/>
       <c r="C55" s="66" t="s">
         <v>219</v>
       </c>
@@ -15291,8 +15295,8 @@
       </c>
     </row>
     <row r="56" spans="1:12" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="208"/>
-      <c r="B56" s="210"/>
+      <c r="A56" s="221"/>
+      <c r="B56" s="211"/>
       <c r="C56" s="152" t="s">
         <v>222</v>
       </c>
@@ -15310,8 +15314,8 @@
       <c r="L56" s="107"/>
     </row>
     <row r="57" spans="1:12" ht="22.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="208"/>
-      <c r="B57" s="203" t="s">
+      <c r="A57" s="221"/>
+      <c r="B57" s="209" t="s">
         <v>223</v>
       </c>
       <c r="C57" s="80" t="s">
@@ -15335,8 +15339,8 @@
       <c r="L57" s="164"/>
     </row>
     <row r="58" spans="1:12" ht="22.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="208"/>
-      <c r="B58" s="204"/>
+      <c r="A58" s="221"/>
+      <c r="B58" s="210"/>
       <c r="C58" s="96" t="s">
         <v>227</v>
       </c>
@@ -15366,8 +15370,8 @@
       </c>
     </row>
     <row r="59" spans="1:12" ht="64.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="208"/>
-      <c r="B59" s="204"/>
+      <c r="A59" s="221"/>
+      <c r="B59" s="210"/>
       <c r="C59" s="96" t="s">
         <v>230</v>
       </c>
@@ -15393,8 +15397,8 @@
       </c>
     </row>
     <row r="60" spans="1:12" ht="31" x14ac:dyDescent="0.2">
-      <c r="A60" s="208"/>
-      <c r="B60" s="204"/>
+      <c r="A60" s="221"/>
+      <c r="B60" s="210"/>
       <c r="C60" s="66" t="s">
         <v>232</v>
       </c>
@@ -15416,8 +15420,8 @@
       <c r="L60" s="104"/>
     </row>
     <row r="61" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="208"/>
-      <c r="B61" s="204"/>
+      <c r="A61" s="221"/>
+      <c r="B61" s="210"/>
       <c r="C61" s="96" t="s">
         <v>439</v>
       </c>
@@ -15439,8 +15443,8 @@
       <c r="L61" s="104"/>
     </row>
     <row r="62" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="208"/>
-      <c r="B62" s="204"/>
+      <c r="A62" s="221"/>
+      <c r="B62" s="210"/>
       <c r="C62" s="96" t="s">
         <v>236</v>
       </c>
@@ -15462,8 +15466,8 @@
       <c r="L62" s="104"/>
     </row>
     <row r="63" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="208"/>
-      <c r="B63" s="210"/>
+      <c r="A63" s="221"/>
+      <c r="B63" s="211"/>
       <c r="C63" s="152" t="s">
         <v>237</v>
       </c>
@@ -15485,8 +15489,8 @@
       <c r="L63" s="169"/>
     </row>
     <row r="64" spans="1:12" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="208"/>
-      <c r="B64" s="203" t="s">
+      <c r="A64" s="221"/>
+      <c r="B64" s="209" t="s">
         <v>238</v>
       </c>
       <c r="C64" s="110" t="s">
@@ -15518,8 +15522,8 @@
       </c>
     </row>
     <row r="65" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="208"/>
-      <c r="B65" s="204"/>
+      <c r="A65" s="221"/>
+      <c r="B65" s="210"/>
       <c r="C65" s="96" t="s">
         <v>241</v>
       </c>
@@ -15549,8 +15553,8 @@
       </c>
     </row>
     <row r="66" spans="1:12" ht="34.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="208"/>
-      <c r="B66" s="204"/>
+      <c r="A66" s="221"/>
+      <c r="B66" s="210"/>
       <c r="C66" s="96" t="s">
         <v>242</v>
       </c>
@@ -15572,8 +15576,8 @@
       <c r="L66" s="104"/>
     </row>
     <row r="67" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="208"/>
-      <c r="B67" s="204"/>
+      <c r="A67" s="221"/>
+      <c r="B67" s="210"/>
       <c r="C67" s="96" t="s">
         <v>243</v>
       </c>
@@ -15599,8 +15603,8 @@
       </c>
     </row>
     <row r="68" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="208"/>
-      <c r="B68" s="204"/>
+      <c r="A68" s="221"/>
+      <c r="B68" s="210"/>
       <c r="C68" s="96" t="s">
         <v>245</v>
       </c>
@@ -15626,8 +15630,8 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="208"/>
-      <c r="B69" s="204"/>
+      <c r="A69" s="221"/>
+      <c r="B69" s="210"/>
       <c r="C69" s="96" t="s">
         <v>247</v>
       </c>
@@ -15657,8 +15661,8 @@
       </c>
     </row>
     <row r="70" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="208"/>
-      <c r="B70" s="204"/>
+      <c r="A70" s="221"/>
+      <c r="B70" s="210"/>
       <c r="C70" s="96" t="s">
         <v>248</v>
       </c>
@@ -15688,8 +15692,8 @@
       </c>
     </row>
     <row r="71" spans="1:12" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="209"/>
-      <c r="B71" s="205"/>
+      <c r="A71" s="222"/>
+      <c r="B71" s="218"/>
       <c r="C71" s="105" t="s">
         <v>249</v>
       </c>
@@ -15720,6 +15724,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B64:B71"/>
+    <mergeCell ref="G53:G54"/>
+    <mergeCell ref="A5:A71"/>
+    <mergeCell ref="B28:B38"/>
+    <mergeCell ref="B39:B43"/>
+    <mergeCell ref="B44:B50"/>
+    <mergeCell ref="B51:B56"/>
+    <mergeCell ref="B57:B63"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="B5:B15"/>
     <mergeCell ref="B16:B21"/>
@@ -15728,14 +15740,6 @@
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="G2:G4"/>
-    <mergeCell ref="B64:B71"/>
-    <mergeCell ref="G53:G54"/>
-    <mergeCell ref="A5:A71"/>
-    <mergeCell ref="B28:B38"/>
-    <mergeCell ref="B39:B43"/>
-    <mergeCell ref="B44:B50"/>
-    <mergeCell ref="B51:B56"/>
-    <mergeCell ref="B57:B63"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:E5 E6:E65 D6:D71 E67 E69 E71">
     <cfRule type="cellIs" dxfId="50" priority="31" operator="equal">
@@ -15934,8 +15938,8 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="217"/>
-      <c r="B3" s="219"/>
+      <c r="A3" s="212"/>
+      <c r="B3" s="214"/>
       <c r="C3" s="224"/>
       <c r="D3" s="16" t="str">
         <f>'Scenario overview'!B18</f>
@@ -15945,8 +15949,8 @@
         <f>'Scenario overview'!B17</f>
         <v>COUNTRY NAME</v>
       </c>
-      <c r="F3" s="221"/>
-      <c r="G3" s="221"/>
+      <c r="F3" s="216"/>
+      <c r="G3" s="216"/>
       <c r="H3" s="235"/>
       <c r="I3" s="235"/>
       <c r="J3" s="235"/>
@@ -15959,7 +15963,7 @@
       <c r="C4" s="225"/>
       <c r="D4" s="31"/>
       <c r="E4" s="31"/>
-      <c r="F4" s="222"/>
+      <c r="F4" s="217"/>
       <c r="G4" s="227"/>
       <c r="H4" s="236"/>
       <c r="I4" s="236"/>
@@ -15968,7 +15972,7 @@
       <c r="L4" s="239"/>
     </row>
     <row r="5" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="207" t="s">
+      <c r="A5" s="220" t="s">
         <v>250</v>
       </c>
       <c r="B5" s="73" t="s">
@@ -15997,8 +16001,8 @@
       <c r="L5" s="79"/>
     </row>
     <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="208"/>
-      <c r="B6" s="203" t="s">
+      <c r="A6" s="221"/>
+      <c r="B6" s="209" t="s">
         <v>256</v>
       </c>
       <c r="C6" s="80" t="s">
@@ -16026,8 +16030,8 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="208"/>
-      <c r="B7" s="212"/>
+      <c r="A7" s="221"/>
+      <c r="B7" s="207"/>
       <c r="C7" s="66" t="s">
         <v>260</v>
       </c>
@@ -16057,8 +16061,8 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="208"/>
-      <c r="B8" s="212"/>
+      <c r="A8" s="221"/>
+      <c r="B8" s="207"/>
       <c r="C8" s="66" t="s">
         <v>263</v>
       </c>
@@ -16084,8 +16088,8 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="208"/>
-      <c r="B9" s="212"/>
+      <c r="A9" s="221"/>
+      <c r="B9" s="207"/>
       <c r="C9" s="66" t="s">
         <v>266</v>
       </c>
@@ -16111,8 +16115,8 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="31.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="208"/>
-      <c r="B10" s="212"/>
+      <c r="A10" s="221"/>
+      <c r="B10" s="207"/>
       <c r="C10" s="66" t="s">
         <v>269</v>
       </c>
@@ -16142,8 +16146,8 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="208"/>
-      <c r="B11" s="212"/>
+      <c r="A11" s="221"/>
+      <c r="B11" s="207"/>
       <c r="C11" s="66" t="s">
         <v>271</v>
       </c>
@@ -16173,8 +16177,8 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="208"/>
-      <c r="B12" s="212"/>
+      <c r="A12" s="221"/>
+      <c r="B12" s="207"/>
       <c r="C12" s="66" t="s">
         <v>275</v>
       </c>
@@ -16200,8 +16204,8 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="208"/>
-      <c r="B13" s="212"/>
+      <c r="A13" s="221"/>
+      <c r="B13" s="207"/>
       <c r="C13" s="66" t="s">
         <v>278</v>
       </c>
@@ -16227,8 +16231,8 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="208"/>
-      <c r="B14" s="212"/>
+      <c r="A14" s="221"/>
+      <c r="B14" s="207"/>
       <c r="C14" s="66" t="s">
         <v>279</v>
       </c>
@@ -16254,8 +16258,8 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="208"/>
-      <c r="B15" s="212"/>
+      <c r="A15" s="221"/>
+      <c r="B15" s="207"/>
       <c r="C15" s="66" t="s">
         <v>282</v>
       </c>
@@ -16281,8 +16285,8 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="208"/>
-      <c r="B16" s="212"/>
+      <c r="A16" s="221"/>
+      <c r="B16" s="207"/>
       <c r="C16" s="66" t="s">
         <v>285</v>
       </c>
@@ -16308,8 +16312,8 @@
       </c>
     </row>
     <row r="17" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="208"/>
-      <c r="B17" s="212"/>
+      <c r="A17" s="221"/>
+      <c r="B17" s="207"/>
       <c r="C17" s="66" t="s">
         <v>287</v>
       </c>
@@ -16339,8 +16343,8 @@
       </c>
     </row>
     <row r="18" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="208"/>
-      <c r="B18" s="212"/>
+      <c r="A18" s="221"/>
+      <c r="B18" s="207"/>
       <c r="C18" s="66" t="s">
         <v>455</v>
       </c>
@@ -16370,8 +16374,8 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="208"/>
-      <c r="B19" s="212"/>
+      <c r="A19" s="221"/>
+      <c r="B19" s="207"/>
       <c r="C19" s="66" t="s">
         <v>293</v>
       </c>
@@ -16391,8 +16395,8 @@
       <c r="L19" s="86"/>
     </row>
     <row r="20" spans="1:17" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="208"/>
-      <c r="B20" s="212"/>
+      <c r="A20" s="221"/>
+      <c r="B20" s="207"/>
       <c r="C20" s="66" t="s">
         <v>295</v>
       </c>
@@ -16412,8 +16416,8 @@
       <c r="L20" s="86"/>
     </row>
     <row r="21" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="208"/>
-      <c r="B21" s="212"/>
+      <c r="A21" s="221"/>
+      <c r="B21" s="207"/>
       <c r="C21" s="66" t="s">
         <v>296</v>
       </c>
@@ -16433,8 +16437,8 @@
       <c r="L21" s="86"/>
     </row>
     <row r="22" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="208"/>
-      <c r="B22" s="212"/>
+      <c r="A22" s="221"/>
+      <c r="B22" s="207"/>
       <c r="C22" s="66" t="s">
         <v>297</v>
       </c>
@@ -16454,8 +16458,8 @@
       <c r="L22" s="86"/>
     </row>
     <row r="23" spans="1:17" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="208"/>
-      <c r="B23" s="212"/>
+      <c r="A23" s="221"/>
+      <c r="B23" s="207"/>
       <c r="C23" s="66" t="s">
         <v>298</v>
       </c>
@@ -16475,8 +16479,8 @@
       <c r="L23" s="86"/>
     </row>
     <row r="24" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="208"/>
-      <c r="B24" s="212"/>
+      <c r="A24" s="221"/>
+      <c r="B24" s="207"/>
       <c r="C24" s="66" t="s">
         <v>300</v>
       </c>
@@ -16496,8 +16500,8 @@
       <c r="L24" s="86"/>
     </row>
     <row r="25" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="208"/>
-      <c r="B25" s="212"/>
+      <c r="A25" s="221"/>
+      <c r="B25" s="207"/>
       <c r="C25" s="66" t="s">
         <v>301</v>
       </c>
@@ -16521,8 +16525,8 @@
       </c>
     </row>
     <row r="26" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="208"/>
-      <c r="B26" s="212"/>
+      <c r="A26" s="221"/>
+      <c r="B26" s="207"/>
       <c r="C26" s="66" t="s">
         <v>304</v>
       </c>
@@ -16546,7 +16550,7 @@
       </c>
     </row>
     <row r="27" spans="1:17" s="8" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="208"/>
+      <c r="A27" s="221"/>
       <c r="B27" s="229"/>
       <c r="C27" s="13" t="s">
         <v>305</v>
@@ -16576,8 +16580,8 @@
       <c r="Q27" s="2"/>
     </row>
     <row r="28" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="208"/>
-      <c r="B28" s="203" t="s">
+      <c r="A28" s="221"/>
+      <c r="B28" s="209" t="s">
         <v>307</v>
       </c>
       <c r="C28" s="80" t="s">
@@ -16609,8 +16613,8 @@
       </c>
     </row>
     <row r="29" spans="1:17" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="208"/>
-      <c r="B29" s="204"/>
+      <c r="A29" s="221"/>
+      <c r="B29" s="210"/>
       <c r="C29" s="66" t="s">
         <v>456</v>
       </c>
@@ -16640,8 +16644,8 @@
       </c>
     </row>
     <row r="30" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="208"/>
-      <c r="B30" s="204"/>
+      <c r="A30" s="221"/>
+      <c r="B30" s="210"/>
       <c r="C30" s="66" t="s">
         <v>312</v>
       </c>
@@ -16671,8 +16675,8 @@
       </c>
     </row>
     <row r="31" spans="1:17" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="208"/>
-      <c r="B31" s="204"/>
+      <c r="A31" s="221"/>
+      <c r="B31" s="210"/>
       <c r="C31" s="66" t="s">
         <v>313</v>
       </c>
@@ -16702,8 +16706,8 @@
       </c>
     </row>
     <row r="32" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="208"/>
-      <c r="B32" s="204"/>
+      <c r="A32" s="221"/>
+      <c r="B32" s="210"/>
       <c r="C32" s="66" t="s">
         <v>316</v>
       </c>
@@ -16733,8 +16737,8 @@
       </c>
     </row>
     <row r="33" spans="1:19" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="208"/>
-      <c r="B33" s="204"/>
+      <c r="A33" s="221"/>
+      <c r="B33" s="210"/>
       <c r="C33" s="66" t="s">
         <v>318</v>
       </c>
@@ -16764,8 +16768,8 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="208"/>
-      <c r="B34" s="204"/>
+      <c r="A34" s="221"/>
+      <c r="B34" s="210"/>
       <c r="C34" s="66" t="s">
         <v>320</v>
       </c>
@@ -16793,8 +16797,8 @@
       </c>
     </row>
     <row r="35" spans="1:19" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="208"/>
-      <c r="B35" s="204"/>
+      <c r="A35" s="221"/>
+      <c r="B35" s="210"/>
       <c r="C35" s="66" t="s">
         <v>321</v>
       </c>
@@ -16822,8 +16826,8 @@
       </c>
     </row>
     <row r="36" spans="1:19" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="208"/>
-      <c r="B36" s="204"/>
+      <c r="A36" s="221"/>
+      <c r="B36" s="210"/>
       <c r="C36" s="66" t="s">
         <v>322</v>
       </c>
@@ -16851,8 +16855,8 @@
       </c>
     </row>
     <row r="37" spans="1:19" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="208"/>
-      <c r="B37" s="204"/>
+      <c r="A37" s="221"/>
+      <c r="B37" s="210"/>
       <c r="C37" s="66" t="s">
         <v>323</v>
       </c>
@@ -16880,8 +16884,8 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="208"/>
-      <c r="B38" s="204"/>
+      <c r="A38" s="221"/>
+      <c r="B38" s="210"/>
       <c r="C38" s="66" t="s">
         <v>324</v>
       </c>
@@ -16899,8 +16903,8 @@
       <c r="L38" s="86"/>
     </row>
     <row r="39" spans="1:19" ht="31.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="208"/>
-      <c r="B39" s="204"/>
+      <c r="A39" s="221"/>
+      <c r="B39" s="210"/>
       <c r="C39" s="66" t="s">
         <v>325</v>
       </c>
@@ -16918,8 +16922,8 @@
       <c r="L39" s="86"/>
     </row>
     <row r="40" spans="1:19" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="208"/>
-      <c r="B40" s="210"/>
+      <c r="A40" s="221"/>
+      <c r="B40" s="211"/>
       <c r="C40" s="152" t="s">
         <v>326</v>
       </c>
@@ -16938,7 +16942,7 @@
     </row>
     <row r="41" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="228"/>
-      <c r="B41" s="203" t="s">
+      <c r="B41" s="209" t="s">
         <v>327</v>
       </c>
       <c r="C41" s="80" t="s">
@@ -16963,7 +16967,7 @@
     </row>
     <row r="42" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="228"/>
-      <c r="B42" s="204"/>
+      <c r="B42" s="210"/>
       <c r="C42" s="66" t="s">
         <v>331</v>
       </c>
@@ -16984,7 +16988,7 @@
     </row>
     <row r="43" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="228"/>
-      <c r="B43" s="204"/>
+      <c r="B43" s="210"/>
       <c r="C43" s="66" t="s">
         <v>332</v>
       </c>
@@ -17015,7 +17019,7 @@
     </row>
     <row r="44" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="228"/>
-      <c r="B44" s="204"/>
+      <c r="B44" s="210"/>
       <c r="C44" s="66" t="s">
         <v>335</v>
       </c>
@@ -17036,7 +17040,7 @@
     </row>
     <row r="45" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="228"/>
-      <c r="B45" s="204"/>
+      <c r="B45" s="210"/>
       <c r="C45" s="66" t="s">
         <v>457</v>
       </c>
@@ -17067,7 +17071,7 @@
     </row>
     <row r="46" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="228"/>
-      <c r="B46" s="204"/>
+      <c r="B46" s="210"/>
       <c r="C46" s="66" t="s">
         <v>458</v>
       </c>
@@ -17096,7 +17100,7 @@
     </row>
     <row r="47" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="228"/>
-      <c r="B47" s="204"/>
+      <c r="B47" s="210"/>
       <c r="C47" s="66" t="s">
         <v>338</v>
       </c>
@@ -17115,7 +17119,7 @@
     </row>
     <row r="48" spans="1:19" s="8" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="228"/>
-      <c r="B48" s="204"/>
+      <c r="B48" s="210"/>
       <c r="C48" s="66" t="s">
         <v>339</v>
       </c>
@@ -17141,7 +17145,7 @@
     </row>
     <row r="49" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="228"/>
-      <c r="B49" s="204"/>
+      <c r="B49" s="210"/>
       <c r="C49" s="66" t="s">
         <v>459</v>
       </c>
@@ -17166,7 +17170,7 @@
     </row>
     <row r="50" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="228"/>
-      <c r="B50" s="204"/>
+      <c r="B50" s="210"/>
       <c r="C50" s="66" t="s">
         <v>342</v>
       </c>
@@ -17185,7 +17189,7 @@
     </row>
     <row r="51" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="228"/>
-      <c r="B51" s="204"/>
+      <c r="B51" s="210"/>
       <c r="C51" s="66" t="s">
         <v>343</v>
       </c>
@@ -17204,7 +17208,7 @@
     </row>
     <row r="52" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="228"/>
-      <c r="B52" s="204"/>
+      <c r="B52" s="210"/>
       <c r="C52" s="66" t="s">
         <v>344</v>
       </c>
@@ -17223,7 +17227,7 @@
     </row>
     <row r="53" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="228"/>
-      <c r="B53" s="205"/>
+      <c r="B53" s="218"/>
       <c r="C53" s="93" t="s">
         <v>345</v>
       </c>
@@ -17241,7 +17245,7 @@
       <c r="L53" s="90"/>
     </row>
     <row r="54" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="209"/>
+      <c r="A54" s="222"/>
       <c r="B54" s="175" t="s">
         <v>346</v>
       </c>
@@ -17997,15 +18001,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="242" t="s">
+      <c r="A1" s="246" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="243"/>
-      <c r="C1" s="243"/>
-      <c r="D1" s="243"/>
-      <c r="E1" s="243"/>
-      <c r="F1" s="243"/>
-      <c r="G1" s="243"/>
+      <c r="B1" s="247"/>
+      <c r="C1" s="247"/>
+      <c r="D1" s="247"/>
+      <c r="E1" s="247"/>
+      <c r="F1" s="247"/>
+      <c r="G1" s="247"/>
       <c r="H1" s="15"/>
       <c r="I1" s="15"/>
       <c r="J1" s="15"/>
@@ -18013,34 +18017,34 @@
       <c r="L1" s="70"/>
     </row>
     <row r="2" spans="1:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="244"/>
-      <c r="B2" s="246"/>
+      <c r="A2" s="248"/>
+      <c r="B2" s="250"/>
       <c r="C2" s="223"/>
       <c r="D2" s="64"/>
       <c r="E2" s="65"/>
       <c r="F2" s="65"/>
-      <c r="G2" s="250" t="s">
+      <c r="G2" s="254" t="s">
         <v>350</v>
       </c>
-      <c r="H2" s="253" t="s">
+      <c r="H2" s="240" t="s">
         <v>88</v>
       </c>
-      <c r="I2" s="253" t="s">
+      <c r="I2" s="240" t="s">
         <v>89</v>
       </c>
-      <c r="J2" s="253" t="s">
+      <c r="J2" s="240" t="s">
         <v>90</v>
       </c>
-      <c r="K2" s="253" t="s">
+      <c r="K2" s="240" t="s">
         <v>91</v>
       </c>
-      <c r="L2" s="256" t="s">
+      <c r="L2" s="243" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="245"/>
-      <c r="B3" s="247"/>
+      <c r="A3" s="249"/>
+      <c r="B3" s="251"/>
       <c r="C3" s="224"/>
       <c r="D3" s="16" t="str">
         <f>'Scenario overview'!B18</f>
@@ -18051,34 +18055,34 @@
         <v>COUNTRY NAME</v>
       </c>
       <c r="F3" s="16"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="254"/>
-      <c r="I3" s="254"/>
-      <c r="J3" s="254"/>
-      <c r="K3" s="254"/>
-      <c r="L3" s="257"/>
+      <c r="G3" s="255"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
+      <c r="L3" s="244"/>
     </row>
     <row r="4" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="245"/>
-      <c r="B4" s="248"/>
-      <c r="C4" s="249"/>
+      <c r="A4" s="249"/>
+      <c r="B4" s="252"/>
+      <c r="C4" s="253"/>
       <c r="D4" s="31"/>
       <c r="E4" s="31"/>
       <c r="F4" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="G4" s="252"/>
-      <c r="H4" s="255"/>
-      <c r="I4" s="255"/>
-      <c r="J4" s="255"/>
-      <c r="K4" s="255"/>
-      <c r="L4" s="258"/>
+      <c r="G4" s="256"/>
+      <c r="H4" s="242"/>
+      <c r="I4" s="242"/>
+      <c r="J4" s="242"/>
+      <c r="K4" s="242"/>
+      <c r="L4" s="245"/>
     </row>
     <row r="5" spans="1:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="240" t="s">
+      <c r="A5" s="257" t="s">
         <v>351</v>
       </c>
-      <c r="B5" s="203" t="s">
+      <c r="B5" s="209" t="s">
         <v>352</v>
       </c>
       <c r="C5" s="80" t="s">
@@ -18110,8 +18114,8 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="240"/>
-      <c r="B6" s="204"/>
+      <c r="A6" s="257"/>
+      <c r="B6" s="210"/>
       <c r="C6" s="66" t="s">
         <v>356</v>
       </c>
@@ -18141,8 +18145,8 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="240"/>
-      <c r="B7" s="205"/>
+      <c r="A7" s="257"/>
+      <c r="B7" s="218"/>
       <c r="C7" s="9" t="s">
         <v>357</v>
       </c>
@@ -18172,8 +18176,8 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="240"/>
-      <c r="B8" s="203" t="s">
+      <c r="A8" s="257"/>
+      <c r="B8" s="209" t="s">
         <v>359</v>
       </c>
       <c r="C8" s="80" t="s">
@@ -18205,8 +18209,8 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="240"/>
-      <c r="B9" s="205"/>
+      <c r="A9" s="257"/>
+      <c r="B9" s="218"/>
       <c r="C9" s="9" t="s">
         <v>363</v>
       </c>
@@ -18236,8 +18240,8 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="240"/>
-      <c r="B10" s="203" t="s">
+      <c r="A10" s="257"/>
+      <c r="B10" s="209" t="s">
         <v>366</v>
       </c>
       <c r="C10" s="80" t="s">
@@ -18269,8 +18273,8 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="31.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="240"/>
-      <c r="B11" s="204"/>
+      <c r="A11" s="257"/>
+      <c r="B11" s="210"/>
       <c r="C11" s="66" t="s">
         <v>370</v>
       </c>
@@ -18292,8 +18296,8 @@
       <c r="L11" s="71"/>
     </row>
     <row r="12" spans="1:12" ht="31.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="240"/>
-      <c r="B12" s="205"/>
+      <c r="A12" s="257"/>
+      <c r="B12" s="218"/>
       <c r="C12" s="9" t="s">
         <v>373</v>
       </c>
@@ -18315,8 +18319,8 @@
       <c r="L12" s="124"/>
     </row>
     <row r="13" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="240"/>
-      <c r="B13" s="203" t="s">
+      <c r="A13" s="257"/>
+      <c r="B13" s="209" t="s">
         <v>375</v>
       </c>
       <c r="C13" s="80" t="s">
@@ -18346,8 +18350,8 @@
       <c r="L13" s="118"/>
     </row>
     <row r="14" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="240"/>
-      <c r="B14" s="204"/>
+      <c r="A14" s="257"/>
+      <c r="B14" s="210"/>
       <c r="C14" s="66" t="s">
         <v>380</v>
       </c>
@@ -18377,8 +18381,8 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="240"/>
-      <c r="B15" s="204"/>
+      <c r="A15" s="257"/>
+      <c r="B15" s="210"/>
       <c r="C15" s="66" t="s">
         <v>382</v>
       </c>
@@ -18408,8 +18412,8 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="240"/>
-      <c r="B16" s="204"/>
+      <c r="A16" s="257"/>
+      <c r="B16" s="210"/>
       <c r="C16" s="66" t="s">
         <v>383</v>
       </c>
@@ -18433,8 +18437,8 @@
       <c r="L16" s="104"/>
     </row>
     <row r="17" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="240"/>
-      <c r="B17" s="204"/>
+      <c r="A17" s="257"/>
+      <c r="B17" s="210"/>
       <c r="C17" s="66" t="s">
         <v>386</v>
       </c>
@@ -18458,8 +18462,8 @@
       <c r="L17" s="104"/>
     </row>
     <row r="18" spans="1:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="240"/>
-      <c r="B18" s="204"/>
+      <c r="A18" s="257"/>
+      <c r="B18" s="210"/>
       <c r="C18" s="98" t="s">
         <v>388</v>
       </c>
@@ -18483,8 +18487,8 @@
       <c r="L18" s="104"/>
     </row>
     <row r="19" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="240"/>
-      <c r="B19" s="204"/>
+      <c r="A19" s="257"/>
+      <c r="B19" s="210"/>
       <c r="C19" s="66" t="s">
         <v>389</v>
       </c>
@@ -18508,8 +18512,8 @@
       <c r="L19" s="104"/>
     </row>
     <row r="20" spans="1:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="240"/>
-      <c r="B20" s="204"/>
+      <c r="A20" s="257"/>
+      <c r="B20" s="210"/>
       <c r="C20" s="66" t="s">
         <v>466</v>
       </c>
@@ -18533,8 +18537,8 @@
       <c r="L20" s="104"/>
     </row>
     <row r="21" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="240"/>
-      <c r="B21" s="204"/>
+      <c r="A21" s="257"/>
+      <c r="B21" s="210"/>
       <c r="C21" s="66" t="s">
         <v>392</v>
       </c>
@@ -18558,8 +18562,8 @@
       <c r="L21" s="104"/>
     </row>
     <row r="22" spans="1:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="240"/>
-      <c r="B22" s="204"/>
+      <c r="A22" s="257"/>
+      <c r="B22" s="210"/>
       <c r="C22" s="66" t="s">
         <v>393</v>
       </c>
@@ -18587,8 +18591,8 @@
       <c r="L22" s="104"/>
     </row>
     <row r="23" spans="1:12" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="240"/>
-      <c r="B23" s="205"/>
+      <c r="A23" s="257"/>
+      <c r="B23" s="218"/>
       <c r="C23" s="9" t="s">
         <v>467</v>
       </c>
@@ -18618,8 +18622,8 @@
       </c>
     </row>
     <row r="24" spans="1:12" ht="31.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="240"/>
-      <c r="B24" s="203" t="s">
+      <c r="A24" s="257"/>
+      <c r="B24" s="209" t="s">
         <v>397</v>
       </c>
       <c r="C24" s="80" t="s">
@@ -18649,8 +18653,8 @@
       <c r="L24" s="118"/>
     </row>
     <row r="25" spans="1:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="240"/>
-      <c r="B25" s="204"/>
+      <c r="A25" s="257"/>
+      <c r="B25" s="210"/>
       <c r="C25" s="66" t="s">
         <v>399</v>
       </c>
@@ -18678,8 +18682,8 @@
       <c r="L25" s="104"/>
     </row>
     <row r="26" spans="1:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="240"/>
-      <c r="B26" s="204"/>
+      <c r="A26" s="257"/>
+      <c r="B26" s="210"/>
       <c r="C26" s="66" t="s">
         <v>400</v>
       </c>
@@ -18707,8 +18711,8 @@
       <c r="L26" s="104"/>
     </row>
     <row r="27" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="240"/>
-      <c r="B27" s="204"/>
+      <c r="A27" s="257"/>
+      <c r="B27" s="210"/>
       <c r="C27" s="66" t="s">
         <v>402</v>
       </c>
@@ -18736,8 +18740,8 @@
       <c r="L27" s="104"/>
     </row>
     <row r="28" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="240"/>
-      <c r="B28" s="204"/>
+      <c r="A28" s="257"/>
+      <c r="B28" s="210"/>
       <c r="C28" s="66" t="s">
         <v>403</v>
       </c>
@@ -18765,8 +18769,8 @@
       <c r="L28" s="104"/>
     </row>
     <row r="29" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="240"/>
-      <c r="B29" s="204"/>
+      <c r="A29" s="257"/>
+      <c r="B29" s="210"/>
       <c r="C29" s="66" t="s">
         <v>405</v>
       </c>
@@ -18788,8 +18792,8 @@
       <c r="L29" s="104"/>
     </row>
     <row r="30" spans="1:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="240"/>
-      <c r="B30" s="204"/>
+      <c r="A30" s="257"/>
+      <c r="B30" s="210"/>
       <c r="C30" s="66" t="s">
         <v>407</v>
       </c>
@@ -18811,8 +18815,8 @@
       <c r="L30" s="104"/>
     </row>
     <row r="31" spans="1:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="240"/>
-      <c r="B31" s="204"/>
+      <c r="A31" s="257"/>
+      <c r="B31" s="210"/>
       <c r="C31" s="66" t="s">
         <v>393</v>
       </c>
@@ -18842,8 +18846,8 @@
       </c>
     </row>
     <row r="32" spans="1:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="240"/>
-      <c r="B32" s="204"/>
+      <c r="A32" s="257"/>
+      <c r="B32" s="210"/>
       <c r="C32" s="66" t="s">
         <v>410</v>
       </c>
@@ -18871,8 +18875,8 @@
       <c r="L32" s="104"/>
     </row>
     <row r="33" spans="1:12" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="240"/>
-      <c r="B33" s="205"/>
+      <c r="A33" s="257"/>
+      <c r="B33" s="218"/>
       <c r="C33" s="9" t="s">
         <v>412</v>
       </c>
@@ -18894,8 +18898,8 @@
       <c r="L33" s="117"/>
     </row>
     <row r="34" spans="1:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="240"/>
-      <c r="B34" s="203" t="s">
+      <c r="A34" s="257"/>
+      <c r="B34" s="209" t="s">
         <v>415</v>
       </c>
       <c r="C34" s="127" t="s">
@@ -18925,8 +18929,8 @@
       </c>
     </row>
     <row r="35" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="240"/>
-      <c r="B35" s="204"/>
+      <c r="A35" s="257"/>
+      <c r="B35" s="210"/>
       <c r="C35" s="122" t="s">
         <v>418</v>
       </c>
@@ -18954,8 +18958,8 @@
       </c>
     </row>
     <row r="36" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="240"/>
-      <c r="B36" s="204"/>
+      <c r="A36" s="257"/>
+      <c r="B36" s="210"/>
       <c r="C36" s="66" t="s">
         <v>419</v>
       </c>
@@ -18983,8 +18987,8 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="240"/>
-      <c r="B37" s="205"/>
+      <c r="A37" s="257"/>
+      <c r="B37" s="218"/>
       <c r="C37" s="9" t="s">
         <v>421</v>
       </c>
@@ -19012,7 +19016,7 @@
       </c>
     </row>
     <row r="38" spans="1:12" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="241"/>
+      <c r="A38" s="258"/>
       <c r="B38" s="73" t="s">
         <v>422</v>
       </c>
@@ -19046,16 +19050,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="G2:G4"/>
     <mergeCell ref="A5:A38"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B9"/>
@@ -19063,6 +19057,16 @@
     <mergeCell ref="B13:B23"/>
     <mergeCell ref="B24:B33"/>
     <mergeCell ref="B34:B37"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
   </mergeCells>
   <conditionalFormatting sqref="D3:F38">
     <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
@@ -19138,46 +19142,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="263" t="s">
+      <c r="A1" s="267" t="s">
         <v>425</v>
       </c>
-      <c r="B1" s="264"/>
-      <c r="C1" s="259" t="s">
+      <c r="B1" s="268"/>
+      <c r="C1" s="263" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="259"/>
-      <c r="E1" s="259"/>
-      <c r="F1" s="259"/>
-      <c r="G1" s="259"/>
+      <c r="D1" s="263"/>
+      <c r="E1" s="263"/>
+      <c r="F1" s="263"/>
+      <c r="G1" s="263"/>
       <c r="H1" s="2"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="265" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="261" t="s">
+      <c r="B2" s="265" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="260"/>
-      <c r="D2" s="259"/>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="259"/>
+      <c r="C2" s="264"/>
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
+      <c r="G2" s="263"/>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="261"/>
-      <c r="B3" s="261"/>
-      <c r="C3" s="260"/>
-      <c r="D3" s="259"/>
-      <c r="E3" s="259"/>
-      <c r="F3" s="259"/>
-      <c r="G3" s="259"/>
+      <c r="A3" s="265"/>
+      <c r="B3" s="265"/>
+      <c r="C3" s="264"/>
+      <c r="D3" s="263"/>
+      <c r="E3" s="263"/>
+      <c r="F3" s="263"/>
+      <c r="G3" s="263"/>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="262"/>
-      <c r="B4" s="262"/>
+      <c r="A4" s="266"/>
+      <c r="B4" s="266"/>
       <c r="C4" s="188" t="str">
         <f>'Tier overview'!A4</f>
         <v>Minimum</v>
@@ -19200,10 +19204,10 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="207" t="s">
+      <c r="A5" s="220" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="211" t="s">
+      <c r="B5" s="206" t="s">
         <v>94</v>
       </c>
       <c r="C5" s="54" t="str">
@@ -19232,8 +19236,8 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="208"/>
-      <c r="B6" s="212"/>
+      <c r="A6" s="221"/>
+      <c r="B6" s="207"/>
       <c r="C6" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E6,TREATMENT!$C6," ")</f>
         <v xml:space="preserve"> </v>
@@ -19260,8 +19264,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="208"/>
-      <c r="B7" s="212"/>
+      <c r="A7" s="221"/>
+      <c r="B7" s="207"/>
       <c r="C7" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E7,TREATMENT!$C7," ")</f>
         <v xml:space="preserve"> </v>
@@ -19288,8 +19292,8 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="208"/>
-      <c r="B8" s="212"/>
+      <c r="A8" s="221"/>
+      <c r="B8" s="207"/>
       <c r="C8" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E8,TREATMENT!$C8," ")</f>
         <v xml:space="preserve"> </v>
@@ -19316,8 +19320,8 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="208"/>
-      <c r="B9" s="212"/>
+      <c r="A9" s="221"/>
+      <c r="B9" s="207"/>
       <c r="C9" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E9,TREATMENT!$C9," ")</f>
         <v xml:space="preserve"> </v>
@@ -19344,8 +19348,8 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="208"/>
-      <c r="B10" s="212"/>
+      <c r="A10" s="221"/>
+      <c r="B10" s="207"/>
       <c r="C10" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E10,TREATMENT!$C10," ")</f>
         <v xml:space="preserve"> </v>
@@ -19372,8 +19376,8 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="208"/>
-      <c r="B11" s="212"/>
+      <c r="A11" s="221"/>
+      <c r="B11" s="207"/>
       <c r="C11" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E11,TREATMENT!$C11," ")</f>
         <v xml:space="preserve"> </v>
@@ -19400,8 +19404,8 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="208"/>
-      <c r="B12" s="212"/>
+      <c r="A12" s="221"/>
+      <c r="B12" s="207"/>
       <c r="C12" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E12,TREATMENT!$C12," ")</f>
         <v xml:space="preserve"> </v>
@@ -19428,8 +19432,8 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="208"/>
-      <c r="B13" s="212"/>
+      <c r="A13" s="221"/>
+      <c r="B13" s="207"/>
       <c r="C13" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E13,TREATMENT!$C13," ")</f>
         <v xml:space="preserve"> </v>
@@ -19456,8 +19460,8 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="208"/>
-      <c r="B14" s="212"/>
+      <c r="A14" s="221"/>
+      <c r="B14" s="207"/>
       <c r="C14" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E14,TREATMENT!$C14," ")</f>
         <v xml:space="preserve"> </v>
@@ -19484,8 +19488,8 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="208"/>
-      <c r="B15" s="213"/>
+      <c r="A15" s="221"/>
+      <c r="B15" s="208"/>
       <c r="C15" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E15,TREATMENT!$C15," ")</f>
         <v xml:space="preserve"> </v>
@@ -19512,8 +19516,8 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="208"/>
-      <c r="B16" s="203" t="s">
+      <c r="A16" s="221"/>
+      <c r="B16" s="209" t="s">
         <v>123</v>
       </c>
       <c r="C16" s="54" t="str">
@@ -19542,8 +19546,8 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="208"/>
-      <c r="B17" s="204"/>
+      <c r="A17" s="221"/>
+      <c r="B17" s="210"/>
       <c r="C17" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E17,TREATMENT!$C17," ")</f>
         <v xml:space="preserve"> </v>
@@ -19570,8 +19574,8 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="208"/>
-      <c r="B18" s="204"/>
+      <c r="A18" s="221"/>
+      <c r="B18" s="210"/>
       <c r="C18" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E18,TREATMENT!$C18," ")</f>
         <v xml:space="preserve"> </v>
@@ -19598,8 +19602,8 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="208"/>
-      <c r="B19" s="204"/>
+      <c r="A19" s="221"/>
+      <c r="B19" s="210"/>
       <c r="C19" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E19,TREATMENT!$C19," ")</f>
         <v xml:space="preserve"> </v>
@@ -19626,8 +19630,8 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="208"/>
-      <c r="B20" s="204"/>
+      <c r="A20" s="221"/>
+      <c r="B20" s="210"/>
       <c r="C20" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E20,TREATMENT!$C20," ")</f>
         <v xml:space="preserve"> </v>
@@ -19654,8 +19658,8 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="208"/>
-      <c r="B21" s="210"/>
+      <c r="A21" s="221"/>
+      <c r="B21" s="211"/>
       <c r="C21" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E21,TREATMENT!$C21," ")</f>
         <v xml:space="preserve"> </v>
@@ -19682,8 +19686,8 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="208"/>
-      <c r="B22" s="203" t="s">
+      <c r="A22" s="221"/>
+      <c r="B22" s="209" t="s">
         <v>146</v>
       </c>
       <c r="C22" s="54" t="str">
@@ -19712,8 +19716,8 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="208"/>
-      <c r="B23" s="204"/>
+      <c r="A23" s="221"/>
+      <c r="B23" s="210"/>
       <c r="C23" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E23,TREATMENT!$C23," ")</f>
         <v xml:space="preserve"> </v>
@@ -19740,8 +19744,8 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="208"/>
-      <c r="B24" s="204"/>
+      <c r="A24" s="221"/>
+      <c r="B24" s="210"/>
       <c r="C24" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E24,TREATMENT!$C24," ")</f>
         <v xml:space="preserve"> </v>
@@ -19768,8 +19772,8 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="208"/>
-      <c r="B25" s="204"/>
+      <c r="A25" s="221"/>
+      <c r="B25" s="210"/>
       <c r="C25" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E25,TREATMENT!$C25," ")</f>
         <v xml:space="preserve"> </v>
@@ -19796,8 +19800,8 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A26" s="208"/>
-      <c r="B26" s="204"/>
+      <c r="A26" s="221"/>
+      <c r="B26" s="210"/>
       <c r="C26" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E26,TREATMENT!$C26," ")</f>
         <v xml:space="preserve"> </v>
@@ -19824,8 +19828,8 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="208"/>
-      <c r="B27" s="210"/>
+      <c r="A27" s="221"/>
+      <c r="B27" s="211"/>
       <c r="C27" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E27,TREATMENT!$C27," ")</f>
         <v xml:space="preserve"> </v>
@@ -19852,8 +19856,8 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" s="208"/>
-      <c r="B28" s="203" t="s">
+      <c r="A28" s="221"/>
+      <c r="B28" s="209" t="s">
         <v>155</v>
       </c>
       <c r="C28" s="54" t="str">
@@ -19882,8 +19886,8 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A29" s="208"/>
-      <c r="B29" s="204"/>
+      <c r="A29" s="221"/>
+      <c r="B29" s="210"/>
       <c r="C29" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E29,TREATMENT!$C29," ")</f>
         <v xml:space="preserve"> </v>
@@ -19910,8 +19914,8 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A30" s="208"/>
-      <c r="B30" s="204"/>
+      <c r="A30" s="221"/>
+      <c r="B30" s="210"/>
       <c r="C30" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E30,TREATMENT!$C30," ")</f>
         <v xml:space="preserve"> </v>
@@ -19938,8 +19942,8 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A31" s="208"/>
-      <c r="B31" s="204"/>
+      <c r="A31" s="221"/>
+      <c r="B31" s="210"/>
       <c r="C31" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E31,TREATMENT!$C31," ")</f>
         <v xml:space="preserve"> </v>
@@ -19966,8 +19970,8 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A32" s="208"/>
-      <c r="B32" s="204"/>
+      <c r="A32" s="221"/>
+      <c r="B32" s="210"/>
       <c r="C32" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E32,TREATMENT!$C32," ")</f>
         <v xml:space="preserve"> </v>
@@ -19994,8 +19998,8 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A33" s="208"/>
-      <c r="B33" s="204"/>
+      <c r="A33" s="221"/>
+      <c r="B33" s="210"/>
       <c r="C33" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E33,TREATMENT!$C33," ")</f>
         <v xml:space="preserve"> </v>
@@ -20022,8 +20026,8 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A34" s="208"/>
-      <c r="B34" s="204"/>
+      <c r="A34" s="221"/>
+      <c r="B34" s="210"/>
       <c r="C34" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E34,TREATMENT!$C34," ")</f>
         <v xml:space="preserve"> </v>
@@ -20050,8 +20054,8 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A35" s="208"/>
-      <c r="B35" s="204"/>
+      <c r="A35" s="221"/>
+      <c r="B35" s="210"/>
       <c r="C35" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E35,TREATMENT!$C35," ")</f>
         <v xml:space="preserve"> </v>
@@ -20078,8 +20082,8 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A36" s="208"/>
-      <c r="B36" s="204"/>
+      <c r="A36" s="221"/>
+      <c r="B36" s="210"/>
       <c r="C36" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E36,TREATMENT!$C36," ")</f>
         <v xml:space="preserve"> </v>
@@ -20106,8 +20110,8 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A37" s="208"/>
-      <c r="B37" s="204"/>
+      <c r="A37" s="221"/>
+      <c r="B37" s="210"/>
       <c r="C37" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E37,TREATMENT!$C37," ")</f>
         <v xml:space="preserve"> </v>
@@ -20134,8 +20138,8 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="208"/>
-      <c r="B38" s="210"/>
+      <c r="A38" s="221"/>
+      <c r="B38" s="211"/>
       <c r="C38" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E38,TREATMENT!$C38," ")</f>
         <v xml:space="preserve"> </v>
@@ -20162,8 +20166,8 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A39" s="208"/>
-      <c r="B39" s="211" t="s">
+      <c r="A39" s="221"/>
+      <c r="B39" s="206" t="s">
         <v>175</v>
       </c>
       <c r="C39" s="54" t="str">
@@ -20192,8 +20196,8 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A40" s="208"/>
-      <c r="B40" s="212"/>
+      <c r="A40" s="221"/>
+      <c r="B40" s="207"/>
       <c r="C40" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E40,TREATMENT!$C40," ")</f>
         <v xml:space="preserve"> </v>
@@ -20220,8 +20224,8 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A41" s="208"/>
-      <c r="B41" s="212"/>
+      <c r="A41" s="221"/>
+      <c r="B41" s="207"/>
       <c r="C41" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E41,TREATMENT!$C41," ")</f>
         <v xml:space="preserve"> </v>
@@ -20248,8 +20252,8 @@
       </c>
     </row>
     <row r="42" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A42" s="208"/>
-      <c r="B42" s="212"/>
+      <c r="A42" s="221"/>
+      <c r="B42" s="207"/>
       <c r="C42" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E42,TREATMENT!$C42," ")</f>
         <v xml:space="preserve"> </v>
@@ -20276,8 +20280,8 @@
       </c>
     </row>
     <row r="43" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="208"/>
-      <c r="B43" s="213"/>
+      <c r="A43" s="221"/>
+      <c r="B43" s="208"/>
       <c r="C43" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E43,TREATMENT!$C43," ")</f>
         <v xml:space="preserve"> </v>
@@ -20304,8 +20308,8 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A44" s="208"/>
-      <c r="B44" s="211" t="s">
+      <c r="A44" s="221"/>
+      <c r="B44" s="206" t="s">
         <v>194</v>
       </c>
       <c r="C44" s="54" t="str">
@@ -20334,8 +20338,8 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A45" s="208"/>
-      <c r="B45" s="212"/>
+      <c r="A45" s="221"/>
+      <c r="B45" s="207"/>
       <c r="C45" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E45,TREATMENT!$C45," ")</f>
         <v xml:space="preserve"> </v>
@@ -20362,8 +20366,8 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A46" s="208"/>
-      <c r="B46" s="212"/>
+      <c r="A46" s="221"/>
+      <c r="B46" s="207"/>
       <c r="C46" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E46,TREATMENT!$C46," ")</f>
         <v xml:space="preserve"> </v>
@@ -20390,8 +20394,8 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A47" s="208"/>
-      <c r="B47" s="212"/>
+      <c r="A47" s="221"/>
+      <c r="B47" s="207"/>
       <c r="C47" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E47,TREATMENT!$C47," ")</f>
         <v xml:space="preserve"> </v>
@@ -20418,8 +20422,8 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A48" s="208"/>
-      <c r="B48" s="212"/>
+      <c r="A48" s="221"/>
+      <c r="B48" s="207"/>
       <c r="C48" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E48,TREATMENT!$C48," ")</f>
         <v xml:space="preserve"> </v>
@@ -20446,8 +20450,8 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A49" s="208"/>
-      <c r="B49" s="212"/>
+      <c r="A49" s="221"/>
+      <c r="B49" s="207"/>
       <c r="C49" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E49,TREATMENT!$C49," ")</f>
         <v xml:space="preserve"> </v>
@@ -20474,8 +20478,8 @@
       </c>
     </row>
     <row r="50" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="208"/>
-      <c r="B50" s="213"/>
+      <c r="A50" s="221"/>
+      <c r="B50" s="208"/>
       <c r="C50" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E50,TREATMENT!$C50," ")</f>
         <v xml:space="preserve"> </v>
@@ -20502,8 +20506,8 @@
       </c>
     </row>
     <row r="51" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A51" s="208"/>
-      <c r="B51" s="203" t="s">
+      <c r="A51" s="221"/>
+      <c r="B51" s="209" t="s">
         <v>210</v>
       </c>
       <c r="C51" s="54" t="str">
@@ -20532,8 +20536,8 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A52" s="208"/>
-      <c r="B52" s="204"/>
+      <c r="A52" s="221"/>
+      <c r="B52" s="210"/>
       <c r="C52" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E52,TREATMENT!$C52," ")</f>
         <v xml:space="preserve"> </v>
@@ -20560,8 +20564,8 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A53" s="208"/>
-      <c r="B53" s="204"/>
+      <c r="A53" s="221"/>
+      <c r="B53" s="210"/>
       <c r="C53" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E53,TREATMENT!$C53," ")</f>
         <v xml:space="preserve"> </v>
@@ -20588,8 +20592,8 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A54" s="208"/>
-      <c r="B54" s="204"/>
+      <c r="A54" s="221"/>
+      <c r="B54" s="210"/>
       <c r="C54" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E54,TREATMENT!$C54," ")</f>
         <v xml:space="preserve"> </v>
@@ -20616,8 +20620,8 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A55" s="208"/>
-      <c r="B55" s="204"/>
+      <c r="A55" s="221"/>
+      <c r="B55" s="210"/>
       <c r="C55" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E55,TREATMENT!$C55," ")</f>
         <v xml:space="preserve"> </v>
@@ -20644,8 +20648,8 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="208"/>
-      <c r="B56" s="210"/>
+      <c r="A56" s="221"/>
+      <c r="B56" s="211"/>
       <c r="C56" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E56,TREATMENT!$C56," ")</f>
         <v xml:space="preserve"> </v>
@@ -20672,8 +20676,8 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A57" s="208"/>
-      <c r="B57" s="203" t="s">
+      <c r="A57" s="221"/>
+      <c r="B57" s="209" t="s">
         <v>223</v>
       </c>
       <c r="C57" s="54" t="str">
@@ -20702,8 +20706,8 @@
       </c>
     </row>
     <row r="58" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A58" s="208"/>
-      <c r="B58" s="204"/>
+      <c r="A58" s="221"/>
+      <c r="B58" s="210"/>
       <c r="C58" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E58,TREATMENT!$C58," ")</f>
         <v xml:space="preserve"> </v>
@@ -20730,8 +20734,8 @@
       </c>
     </row>
     <row r="59" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A59" s="208"/>
-      <c r="B59" s="204"/>
+      <c r="A59" s="221"/>
+      <c r="B59" s="210"/>
       <c r="C59" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E59,TREATMENT!$C59," ")</f>
         <v xml:space="preserve"> </v>
@@ -20758,8 +20762,8 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A60" s="208"/>
-      <c r="B60" s="204"/>
+      <c r="A60" s="221"/>
+      <c r="B60" s="210"/>
       <c r="C60" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E60,TREATMENT!$C60," ")</f>
         <v xml:space="preserve"> </v>
@@ -20786,8 +20790,8 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A61" s="208"/>
-      <c r="B61" s="204"/>
+      <c r="A61" s="221"/>
+      <c r="B61" s="210"/>
       <c r="C61" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E61,TREATMENT!$C61," ")</f>
         <v xml:space="preserve"> </v>
@@ -20814,8 +20818,8 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A62" s="208"/>
-      <c r="B62" s="204"/>
+      <c r="A62" s="221"/>
+      <c r="B62" s="210"/>
       <c r="C62" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E62,TREATMENT!$C62," ")</f>
         <v xml:space="preserve"> </v>
@@ -20842,8 +20846,8 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="208"/>
-      <c r="B63" s="210"/>
+      <c r="A63" s="221"/>
+      <c r="B63" s="211"/>
       <c r="C63" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E63,TREATMENT!$C63," ")</f>
         <v xml:space="preserve"> </v>
@@ -20870,8 +20874,8 @@
       </c>
     </row>
     <row r="64" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A64" s="208"/>
-      <c r="B64" s="203" t="s">
+      <c r="A64" s="221"/>
+      <c r="B64" s="209" t="s">
         <v>238</v>
       </c>
       <c r="C64" s="54" t="str">
@@ -20900,8 +20904,8 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A65" s="208"/>
-      <c r="B65" s="204"/>
+      <c r="A65" s="221"/>
+      <c r="B65" s="210"/>
       <c r="C65" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E65,TREATMENT!$C65," ")</f>
         <v xml:space="preserve"> </v>
@@ -20928,8 +20932,8 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A66" s="208"/>
-      <c r="B66" s="204"/>
+      <c r="A66" s="221"/>
+      <c r="B66" s="210"/>
       <c r="C66" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E66,TREATMENT!$C66," ")</f>
         <v xml:space="preserve"> </v>
@@ -20956,8 +20960,8 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A67" s="208"/>
-      <c r="B67" s="204"/>
+      <c r="A67" s="221"/>
+      <c r="B67" s="210"/>
       <c r="C67" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E67,TREATMENT!$C67," ")</f>
         <v xml:space="preserve"> </v>
@@ -20984,8 +20988,8 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A68" s="208"/>
-      <c r="B68" s="204"/>
+      <c r="A68" s="221"/>
+      <c r="B68" s="210"/>
       <c r="C68" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E68,TREATMENT!$C68," ")</f>
         <v xml:space="preserve"> </v>
@@ -21012,8 +21016,8 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A69" s="208"/>
-      <c r="B69" s="204"/>
+      <c r="A69" s="221"/>
+      <c r="B69" s="210"/>
       <c r="C69" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E69,TREATMENT!$C69," ")</f>
         <v xml:space="preserve"> </v>
@@ -21040,8 +21044,8 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A70" s="208"/>
-      <c r="B70" s="204"/>
+      <c r="A70" s="221"/>
+      <c r="B70" s="210"/>
       <c r="C70" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E70,TREATMENT!$C70," ")</f>
         <v xml:space="preserve"> </v>
@@ -21068,8 +21072,8 @@
       </c>
     </row>
     <row r="71" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="209"/>
-      <c r="B71" s="205"/>
+      <c r="A71" s="222"/>
+      <c r="B71" s="218"/>
       <c r="C71" s="54" t="str">
         <f>+IF(C$4=TREATMENT!$E71,TREATMENT!$C71," ")</f>
         <v xml:space="preserve"> </v>
@@ -21096,7 +21100,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="265" t="s">
+      <c r="A72" s="259" t="s">
         <v>250</v>
       </c>
       <c r="B72" s="73" t="s">
@@ -21128,8 +21132,8 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73" s="266"/>
-      <c r="B73" s="203" t="s">
+      <c r="A73" s="260"/>
+      <c r="B73" s="209" t="s">
         <v>256</v>
       </c>
       <c r="C73" s="2" t="str">
@@ -21158,8 +21162,8 @@
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74" s="266"/>
-      <c r="B74" s="212"/>
+      <c r="A74" s="260"/>
+      <c r="B74" s="207"/>
       <c r="C74" s="2" t="str">
         <f>+IF(C$4=TESTING!$E7,TESTING!$C7," ")</f>
         <v xml:space="preserve"> </v>
@@ -21186,8 +21190,8 @@
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75" s="266"/>
-      <c r="B75" s="212"/>
+      <c r="A75" s="260"/>
+      <c r="B75" s="207"/>
       <c r="C75" s="2" t="str">
         <f>+IF(C$4=TESTING!$E8,TESTING!$C8," ")</f>
         <v xml:space="preserve"> </v>
@@ -21214,8 +21218,8 @@
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76" s="266"/>
-      <c r="B76" s="212"/>
+      <c r="A76" s="260"/>
+      <c r="B76" s="207"/>
       <c r="C76" s="2" t="str">
         <f>+IF(C$4=TESTING!$E9,TESTING!$C9," ")</f>
         <v xml:space="preserve"> </v>
@@ -21242,8 +21246,8 @@
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77" s="266"/>
-      <c r="B77" s="212"/>
+      <c r="A77" s="260"/>
+      <c r="B77" s="207"/>
       <c r="C77" s="2" t="str">
         <f>+IF(C$4=TESTING!$E10,TESTING!$C10," ")</f>
         <v xml:space="preserve"> </v>
@@ -21270,8 +21274,8 @@
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78" s="266"/>
-      <c r="B78" s="212"/>
+      <c r="A78" s="260"/>
+      <c r="B78" s="207"/>
       <c r="C78" s="2" t="str">
         <f>+IF(C$4=TESTING!$E11,TESTING!$C11," ")</f>
         <v xml:space="preserve"> </v>
@@ -21298,8 +21302,8 @@
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79" s="266"/>
-      <c r="B79" s="212"/>
+      <c r="A79" s="260"/>
+      <c r="B79" s="207"/>
       <c r="C79" s="2" t="str">
         <f>+IF(C$4=TESTING!$E12,TESTING!$C12," ")</f>
         <v xml:space="preserve"> </v>
@@ -21326,8 +21330,8 @@
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A80" s="266"/>
-      <c r="B80" s="212"/>
+      <c r="A80" s="260"/>
+      <c r="B80" s="207"/>
       <c r="C80" s="2" t="str">
         <f>+IF(C$4=TESTING!$E13,TESTING!$C13," ")</f>
         <v xml:space="preserve"> </v>
@@ -21354,8 +21358,8 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" s="266"/>
-      <c r="B81" s="212"/>
+      <c r="A81" s="260"/>
+      <c r="B81" s="207"/>
       <c r="C81" s="2" t="str">
         <f>+IF(C$4=TESTING!$E14,TESTING!$C14," ")</f>
         <v xml:space="preserve"> </v>
@@ -21382,8 +21386,8 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" s="266"/>
-      <c r="B82" s="212"/>
+      <c r="A82" s="260"/>
+      <c r="B82" s="207"/>
       <c r="C82" s="2" t="str">
         <f>+IF(C$4=TESTING!$E15,TESTING!$C15," ")</f>
         <v xml:space="preserve"> </v>
@@ -21410,8 +21414,8 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" s="266"/>
-      <c r="B83" s="212"/>
+      <c r="A83" s="260"/>
+      <c r="B83" s="207"/>
       <c r="C83" s="2" t="str">
         <f>+IF(C$4=TESTING!$E16,TESTING!$C16," ")</f>
         <v xml:space="preserve"> </v>
@@ -21438,8 +21442,8 @@
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84" s="266"/>
-      <c r="B84" s="212"/>
+      <c r="A84" s="260"/>
+      <c r="B84" s="207"/>
       <c r="C84" s="2" t="str">
         <f>+IF(C$4=TESTING!$E17,TESTING!$C17," ")</f>
         <v xml:space="preserve"> </v>
@@ -21466,8 +21470,8 @@
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85" s="266"/>
-      <c r="B85" s="212"/>
+      <c r="A85" s="260"/>
+      <c r="B85" s="207"/>
       <c r="C85" s="2" t="str">
         <f>+IF(C$4=TESTING!$E18,TESTING!$C18," ")</f>
         <v xml:space="preserve"> </v>
@@ -21494,8 +21498,8 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A86" s="266"/>
-      <c r="B86" s="212"/>
+      <c r="A86" s="260"/>
+      <c r="B86" s="207"/>
       <c r="C86" s="2" t="str">
         <f>+IF(C$4=TESTING!$E19,TESTING!$C19," ")</f>
         <v xml:space="preserve"> </v>
@@ -21522,8 +21526,8 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87" s="266"/>
-      <c r="B87" s="212"/>
+      <c r="A87" s="260"/>
+      <c r="B87" s="207"/>
       <c r="C87" s="2" t="str">
         <f>+IF(C$4=TESTING!$E20,TESTING!$C20," ")</f>
         <v xml:space="preserve"> </v>
@@ -21550,8 +21554,8 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A88" s="266"/>
-      <c r="B88" s="212"/>
+      <c r="A88" s="260"/>
+      <c r="B88" s="207"/>
       <c r="C88" s="2" t="str">
         <f>+IF(C$4=TESTING!$E21,TESTING!$C21," ")</f>
         <v xml:space="preserve"> </v>
@@ -21578,8 +21582,8 @@
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89" s="266"/>
-      <c r="B89" s="212"/>
+      <c r="A89" s="260"/>
+      <c r="B89" s="207"/>
       <c r="C89" s="2" t="str">
         <f>+IF(C$4=TESTING!$E22,TESTING!$C22," ")</f>
         <v xml:space="preserve"> </v>
@@ -21606,8 +21610,8 @@
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A90" s="266"/>
-      <c r="B90" s="212"/>
+      <c r="A90" s="260"/>
+      <c r="B90" s="207"/>
       <c r="C90" s="2" t="str">
         <f>+IF(C$4=TESTING!$E23,TESTING!$C23," ")</f>
         <v xml:space="preserve"> </v>
@@ -21634,8 +21638,8 @@
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A91" s="266"/>
-      <c r="B91" s="212"/>
+      <c r="A91" s="260"/>
+      <c r="B91" s="207"/>
       <c r="C91" s="2" t="str">
         <f>+IF(C$4=TESTING!$E24,TESTING!$C24," ")</f>
         <v xml:space="preserve"> </v>
@@ -21662,8 +21666,8 @@
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A92" s="266"/>
-      <c r="B92" s="212"/>
+      <c r="A92" s="260"/>
+      <c r="B92" s="207"/>
       <c r="C92" s="2" t="str">
         <f>+IF(C$4=TESTING!$E25,TESTING!$C25," ")</f>
         <v xml:space="preserve"> </v>
@@ -21690,8 +21694,8 @@
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93" s="266"/>
-      <c r="B93" s="212"/>
+      <c r="A93" s="260"/>
+      <c r="B93" s="207"/>
       <c r="C93" s="2" t="str">
         <f>+IF(C$4=TESTING!$E26,TESTING!$C26," ")</f>
         <v xml:space="preserve"> </v>
@@ -21718,7 +21722,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="266"/>
+      <c r="A94" s="260"/>
       <c r="B94" s="229"/>
       <c r="C94" s="2" t="str">
         <f>+IF(C$4=TESTING!$E27,TESTING!$C27," ")</f>
@@ -21746,8 +21750,8 @@
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A95" s="266"/>
-      <c r="B95" s="203" t="s">
+      <c r="A95" s="260"/>
+      <c r="B95" s="209" t="s">
         <v>307</v>
       </c>
       <c r="C95" s="2" t="str">
@@ -21776,8 +21780,8 @@
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A96" s="266"/>
-      <c r="B96" s="204"/>
+      <c r="A96" s="260"/>
+      <c r="B96" s="210"/>
       <c r="C96" s="2" t="str">
         <f>+IF(C$4=TESTING!$E29,TESTING!$C29," ")</f>
         <v xml:space="preserve"> </v>
@@ -21804,8 +21808,8 @@
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A97" s="266"/>
-      <c r="B97" s="204"/>
+      <c r="A97" s="260"/>
+      <c r="B97" s="210"/>
       <c r="C97" s="2" t="str">
         <f>+IF(C$4=TESTING!$E30,TESTING!$C30," ")</f>
         <v xml:space="preserve"> </v>
@@ -21832,8 +21836,8 @@
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A98" s="266"/>
-      <c r="B98" s="204"/>
+      <c r="A98" s="260"/>
+      <c r="B98" s="210"/>
       <c r="C98" s="2" t="str">
         <f>+IF(C$4=TESTING!$E31,TESTING!$C31," ")</f>
         <v xml:space="preserve"> </v>
@@ -21860,8 +21864,8 @@
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A99" s="266"/>
-      <c r="B99" s="204"/>
+      <c r="A99" s="260"/>
+      <c r="B99" s="210"/>
       <c r="C99" s="2" t="str">
         <f>+IF(C$4=TESTING!$E32,TESTING!$C32," ")</f>
         <v xml:space="preserve"> </v>
@@ -21888,8 +21892,8 @@
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A100" s="266"/>
-      <c r="B100" s="204"/>
+      <c r="A100" s="260"/>
+      <c r="B100" s="210"/>
       <c r="C100" s="2" t="str">
         <f>+IF(C$4=TESTING!$E33,TESTING!$C33," ")</f>
         <v xml:space="preserve"> </v>
@@ -21916,8 +21920,8 @@
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A101" s="266"/>
-      <c r="B101" s="204"/>
+      <c r="A101" s="260"/>
+      <c r="B101" s="210"/>
       <c r="C101" s="2" t="str">
         <f>+IF(C$4=TESTING!$E34,TESTING!$C34," ")</f>
         <v xml:space="preserve"> </v>
@@ -21944,8 +21948,8 @@
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A102" s="266"/>
-      <c r="B102" s="204"/>
+      <c r="A102" s="260"/>
+      <c r="B102" s="210"/>
       <c r="C102" s="2" t="str">
         <f>+IF(C$4=TESTING!$E35,TESTING!$C35," ")</f>
         <v xml:space="preserve"> </v>
@@ -21972,8 +21976,8 @@
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A103" s="266"/>
-      <c r="B103" s="204"/>
+      <c r="A103" s="260"/>
+      <c r="B103" s="210"/>
       <c r="C103" s="2" t="str">
         <f>+IF(C$4=TESTING!$E36,TESTING!$C36," ")</f>
         <v xml:space="preserve"> </v>
@@ -22000,8 +22004,8 @@
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A104" s="266"/>
-      <c r="B104" s="204"/>
+      <c r="A104" s="260"/>
+      <c r="B104" s="210"/>
       <c r="C104" s="2" t="str">
         <f>+IF(C$4=TESTING!$E37,TESTING!$C37," ")</f>
         <v xml:space="preserve"> </v>
@@ -22028,8 +22032,8 @@
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A105" s="266"/>
-      <c r="B105" s="204"/>
+      <c r="A105" s="260"/>
+      <c r="B105" s="210"/>
       <c r="C105" s="2" t="str">
         <f>+IF(C$4=TESTING!$E38,TESTING!$C38," ")</f>
         <v xml:space="preserve"> </v>
@@ -22056,8 +22060,8 @@
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A106" s="266"/>
-      <c r="B106" s="204"/>
+      <c r="A106" s="260"/>
+      <c r="B106" s="210"/>
       <c r="C106" s="2" t="str">
         <f>+IF(C$4=TESTING!$E39,TESTING!$C39," ")</f>
         <v xml:space="preserve"> </v>
@@ -22084,8 +22088,8 @@
       </c>
     </row>
     <row r="107" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="266"/>
-      <c r="B107" s="210"/>
+      <c r="A107" s="260"/>
+      <c r="B107" s="211"/>
       <c r="C107" s="2" t="str">
         <f>+IF(C$4=TESTING!$E40,TESTING!$C40," ")</f>
         <v xml:space="preserve"> </v>
@@ -22112,8 +22116,8 @@
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A108" s="267"/>
-      <c r="B108" s="203" t="s">
+      <c r="A108" s="261"/>
+      <c r="B108" s="209" t="s">
         <v>327</v>
       </c>
       <c r="C108" s="2" t="str">
@@ -22142,8 +22146,8 @@
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A109" s="267"/>
-      <c r="B109" s="204"/>
+      <c r="A109" s="261"/>
+      <c r="B109" s="210"/>
       <c r="C109" s="2" t="str">
         <f>+IF(C$4=TESTING!$E42,TESTING!$C42," ")</f>
         <v xml:space="preserve"> </v>
@@ -22170,8 +22174,8 @@
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A110" s="267"/>
-      <c r="B110" s="204"/>
+      <c r="A110" s="261"/>
+      <c r="B110" s="210"/>
       <c r="C110" s="2" t="str">
         <f>+IF(C$4=TESTING!$E43,TESTING!$C43," ")</f>
         <v xml:space="preserve"> </v>
@@ -22198,8 +22202,8 @@
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A111" s="267"/>
-      <c r="B111" s="204"/>
+      <c r="A111" s="261"/>
+      <c r="B111" s="210"/>
       <c r="C111" s="2" t="str">
         <f>+IF(C$4=TESTING!$E44,TESTING!$C44," ")</f>
         <v xml:space="preserve"> </v>
@@ -22226,8 +22230,8 @@
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A112" s="267"/>
-      <c r="B112" s="204"/>
+      <c r="A112" s="261"/>
+      <c r="B112" s="210"/>
       <c r="C112" s="2" t="str">
         <f>+IF(C$4=TESTING!$E45,TESTING!$C45," ")</f>
         <v xml:space="preserve"> </v>
@@ -22254,8 +22258,8 @@
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A113" s="267"/>
-      <c r="B113" s="204"/>
+      <c r="A113" s="261"/>
+      <c r="B113" s="210"/>
       <c r="C113" s="2" t="str">
         <f>+IF(C$4=TESTING!$E46,TESTING!$C46," ")</f>
         <v xml:space="preserve"> </v>
@@ -22282,8 +22286,8 @@
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A114" s="267"/>
-      <c r="B114" s="204"/>
+      <c r="A114" s="261"/>
+      <c r="B114" s="210"/>
       <c r="C114" s="2" t="str">
         <f>+IF(C$4=TESTING!$E47,TESTING!$C47," ")</f>
         <v xml:space="preserve"> </v>
@@ -22310,8 +22314,8 @@
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A115" s="267"/>
-      <c r="B115" s="204"/>
+      <c r="A115" s="261"/>
+      <c r="B115" s="210"/>
       <c r="C115" s="2" t="str">
         <f>+IF(C$4=TESTING!$E48,TESTING!$C48," ")</f>
         <v xml:space="preserve"> </v>
@@ -22338,8 +22342,8 @@
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A116" s="267"/>
-      <c r="B116" s="204"/>
+      <c r="A116" s="261"/>
+      <c r="B116" s="210"/>
       <c r="C116" s="2" t="str">
         <f>+IF(C$4=TESTING!$E49,TESTING!$C49," ")</f>
         <v xml:space="preserve"> </v>
@@ -22366,8 +22370,8 @@
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A117" s="267"/>
-      <c r="B117" s="204"/>
+      <c r="A117" s="261"/>
+      <c r="B117" s="210"/>
       <c r="C117" s="2" t="str">
         <f>+IF(C$4=TESTING!$E50,TESTING!$C50," ")</f>
         <v xml:space="preserve"> </v>
@@ -22394,8 +22398,8 @@
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A118" s="267"/>
-      <c r="B118" s="204"/>
+      <c r="A118" s="261"/>
+      <c r="B118" s="210"/>
       <c r="C118" s="2" t="str">
         <f>+IF(C$4=TESTING!$E51,TESTING!$C51," ")</f>
         <v xml:space="preserve"> </v>
@@ -22422,8 +22426,8 @@
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A119" s="267"/>
-      <c r="B119" s="204"/>
+      <c r="A119" s="261"/>
+      <c r="B119" s="210"/>
       <c r="C119" s="2" t="str">
         <f>+IF(C$4=TESTING!$E52,TESTING!$C52," ")</f>
         <v xml:space="preserve"> </v>
@@ -22450,8 +22454,8 @@
       </c>
     </row>
     <row r="120" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="267"/>
-      <c r="B120" s="205"/>
+      <c r="A120" s="261"/>
+      <c r="B120" s="218"/>
       <c r="C120" s="2" t="str">
         <f>+IF(C$4=TESTING!$E53,TESTING!$C53," ")</f>
         <v xml:space="preserve"> </v>
@@ -22478,7 +22482,7 @@
       </c>
     </row>
     <row r="121" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="268"/>
+      <c r="A121" s="262"/>
       <c r="B121" s="175" t="s">
         <v>346</v>
       </c>
@@ -22508,10 +22512,10 @@
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A122" s="240" t="s">
+      <c r="A122" s="257" t="s">
         <v>351</v>
       </c>
-      <c r="B122" s="203" t="s">
+      <c r="B122" s="209" t="s">
         <v>352</v>
       </c>
       <c r="C122" s="2" t="str">
@@ -22540,8 +22544,8 @@
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A123" s="240"/>
-      <c r="B123" s="204"/>
+      <c r="A123" s="257"/>
+      <c r="B123" s="210"/>
       <c r="C123" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E6,PREVENTION!$C6," ")</f>
         <v xml:space="preserve"> </v>
@@ -22568,8 +22572,8 @@
       </c>
     </row>
     <row r="124" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="240"/>
-      <c r="B124" s="205"/>
+      <c r="A124" s="257"/>
+      <c r="B124" s="218"/>
       <c r="C124" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E7,PREVENTION!$C7," ")</f>
         <v xml:space="preserve"> </v>
@@ -22596,8 +22600,8 @@
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A125" s="240"/>
-      <c r="B125" s="203" t="s">
+      <c r="A125" s="257"/>
+      <c r="B125" s="209" t="s">
         <v>359</v>
       </c>
       <c r="C125" s="2" t="str">
@@ -22626,8 +22630,8 @@
       </c>
     </row>
     <row r="126" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="240"/>
-      <c r="B126" s="205"/>
+      <c r="A126" s="257"/>
+      <c r="B126" s="218"/>
       <c r="C126" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E9,PREVENTION!$C9," ")</f>
         <v xml:space="preserve"> </v>
@@ -22654,8 +22658,8 @@
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A127" s="240"/>
-      <c r="B127" s="203" t="s">
+      <c r="A127" s="257"/>
+      <c r="B127" s="209" t="s">
         <v>366</v>
       </c>
       <c r="C127" s="2" t="str">
@@ -22684,8 +22688,8 @@
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A128" s="240"/>
-      <c r="B128" s="204"/>
+      <c r="A128" s="257"/>
+      <c r="B128" s="210"/>
       <c r="C128" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E11,PREVENTION!$C11," ")</f>
         <v xml:space="preserve"> </v>
@@ -22712,8 +22716,8 @@
       </c>
     </row>
     <row r="129" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="240"/>
-      <c r="B129" s="205"/>
+      <c r="A129" s="257"/>
+      <c r="B129" s="218"/>
       <c r="C129" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E12,PREVENTION!$C12," ")</f>
         <v xml:space="preserve"> </v>
@@ -22740,8 +22744,8 @@
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A130" s="240"/>
-      <c r="B130" s="203" t="s">
+      <c r="A130" s="257"/>
+      <c r="B130" s="209" t="s">
         <v>375</v>
       </c>
       <c r="C130" s="2" t="str">
@@ -22770,8 +22774,8 @@
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A131" s="240"/>
-      <c r="B131" s="204"/>
+      <c r="A131" s="257"/>
+      <c r="B131" s="210"/>
       <c r="C131" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E14,PREVENTION!$C14," ")</f>
         <v xml:space="preserve"> </v>
@@ -22798,8 +22802,8 @@
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A132" s="240"/>
-      <c r="B132" s="204"/>
+      <c r="A132" s="257"/>
+      <c r="B132" s="210"/>
       <c r="C132" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E15,PREVENTION!$C15," ")</f>
         <v xml:space="preserve"> </v>
@@ -22826,8 +22830,8 @@
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A133" s="240"/>
-      <c r="B133" s="204"/>
+      <c r="A133" s="257"/>
+      <c r="B133" s="210"/>
       <c r="C133" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E16,PREVENTION!$C16," ")</f>
         <v xml:space="preserve"> </v>
@@ -22854,8 +22858,8 @@
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A134" s="240"/>
-      <c r="B134" s="204"/>
+      <c r="A134" s="257"/>
+      <c r="B134" s="210"/>
       <c r="C134" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E17,PREVENTION!$C17," ")</f>
         <v xml:space="preserve"> </v>
@@ -22882,8 +22886,8 @@
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A135" s="240"/>
-      <c r="B135" s="204"/>
+      <c r="A135" s="257"/>
+      <c r="B135" s="210"/>
       <c r="C135" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E18,PREVENTION!$C18," ")</f>
         <v xml:space="preserve"> </v>
@@ -22910,8 +22914,8 @@
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A136" s="240"/>
-      <c r="B136" s="204"/>
+      <c r="A136" s="257"/>
+      <c r="B136" s="210"/>
       <c r="C136" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E19,PREVENTION!$C19," ")</f>
         <v xml:space="preserve"> </v>
@@ -22938,8 +22942,8 @@
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A137" s="240"/>
-      <c r="B137" s="204"/>
+      <c r="A137" s="257"/>
+      <c r="B137" s="210"/>
       <c r="C137" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E20,PREVENTION!$C20," ")</f>
         <v xml:space="preserve"> </v>
@@ -22966,8 +22970,8 @@
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A138" s="240"/>
-      <c r="B138" s="204"/>
+      <c r="A138" s="257"/>
+      <c r="B138" s="210"/>
       <c r="C138" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E21,PREVENTION!$C21," ")</f>
         <v xml:space="preserve"> </v>
@@ -22994,8 +22998,8 @@
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A139" s="240"/>
-      <c r="B139" s="204"/>
+      <c r="A139" s="257"/>
+      <c r="B139" s="210"/>
       <c r="C139" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E22,PREVENTION!$C22," ")</f>
         <v xml:space="preserve"> </v>
@@ -23022,8 +23026,8 @@
       </c>
     </row>
     <row r="140" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="240"/>
-      <c r="B140" s="205"/>
+      <c r="A140" s="257"/>
+      <c r="B140" s="218"/>
       <c r="C140" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E23,PREVENTION!$C23," ")</f>
         <v xml:space="preserve"> </v>
@@ -23050,8 +23054,8 @@
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A141" s="240"/>
-      <c r="B141" s="203" t="s">
+      <c r="A141" s="257"/>
+      <c r="B141" s="209" t="s">
         <v>397</v>
       </c>
       <c r="C141" s="2" t="str">
@@ -23080,8 +23084,8 @@
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A142" s="240"/>
-      <c r="B142" s="204"/>
+      <c r="A142" s="257"/>
+      <c r="B142" s="210"/>
       <c r="C142" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E25,PREVENTION!$C25," ")</f>
         <v xml:space="preserve"> </v>
@@ -23108,8 +23112,8 @@
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A143" s="240"/>
-      <c r="B143" s="204"/>
+      <c r="A143" s="257"/>
+      <c r="B143" s="210"/>
       <c r="C143" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E26,PREVENTION!$C26," ")</f>
         <v xml:space="preserve"> </v>
@@ -23136,8 +23140,8 @@
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A144" s="240"/>
-      <c r="B144" s="204"/>
+      <c r="A144" s="257"/>
+      <c r="B144" s="210"/>
       <c r="C144" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E27,PREVENTION!$C27," ")</f>
         <v xml:space="preserve"> </v>
@@ -23164,8 +23168,8 @@
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A145" s="240"/>
-      <c r="B145" s="204"/>
+      <c r="A145" s="257"/>
+      <c r="B145" s="210"/>
       <c r="C145" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E28,PREVENTION!$C28," ")</f>
         <v xml:space="preserve"> </v>
@@ -23192,8 +23196,8 @@
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A146" s="240"/>
-      <c r="B146" s="204"/>
+      <c r="A146" s="257"/>
+      <c r="B146" s="210"/>
       <c r="C146" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E29,PREVENTION!$C29," ")</f>
         <v xml:space="preserve"> </v>
@@ -23220,8 +23224,8 @@
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A147" s="240"/>
-      <c r="B147" s="204"/>
+      <c r="A147" s="257"/>
+      <c r="B147" s="210"/>
       <c r="C147" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E30,PREVENTION!$C30," ")</f>
         <v xml:space="preserve"> </v>
@@ -23248,8 +23252,8 @@
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A148" s="240"/>
-      <c r="B148" s="204"/>
+      <c r="A148" s="257"/>
+      <c r="B148" s="210"/>
       <c r="C148" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E31,PREVENTION!$C31," ")</f>
         <v xml:space="preserve"> </v>
@@ -23276,8 +23280,8 @@
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A149" s="240"/>
-      <c r="B149" s="204"/>
+      <c r="A149" s="257"/>
+      <c r="B149" s="210"/>
       <c r="C149" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E32,PREVENTION!$C32," ")</f>
         <v xml:space="preserve"> </v>
@@ -23304,8 +23308,8 @@
       </c>
     </row>
     <row r="150" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="240"/>
-      <c r="B150" s="205"/>
+      <c r="A150" s="257"/>
+      <c r="B150" s="218"/>
       <c r="C150" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E33,PREVENTION!$C33," ")</f>
         <v xml:space="preserve"> </v>
@@ -23332,8 +23336,8 @@
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A151" s="240"/>
-      <c r="B151" s="203" t="s">
+      <c r="A151" s="257"/>
+      <c r="B151" s="209" t="s">
         <v>415</v>
       </c>
       <c r="C151" s="2" t="str">
@@ -23362,8 +23366,8 @@
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A152" s="240"/>
-      <c r="B152" s="204"/>
+      <c r="A152" s="257"/>
+      <c r="B152" s="210"/>
       <c r="C152" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E35,PREVENTION!$C35," ")</f>
         <v xml:space="preserve"> </v>
@@ -23390,8 +23394,8 @@
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A153" s="240"/>
-      <c r="B153" s="204"/>
+      <c r="A153" s="257"/>
+      <c r="B153" s="210"/>
       <c r="C153" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E36,PREVENTION!$C36," ")</f>
         <v xml:space="preserve"> </v>
@@ -23418,8 +23422,8 @@
       </c>
     </row>
     <row r="154" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="240"/>
-      <c r="B154" s="205"/>
+      <c r="A154" s="257"/>
+      <c r="B154" s="218"/>
       <c r="C154" s="2" t="str">
         <f>+IF(C$4=PREVENTION!$E37,PREVENTION!$C37," ")</f>
         <v xml:space="preserve"> </v>
@@ -23446,7 +23450,7 @@
       </c>
     </row>
     <row r="155" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="241"/>
+      <c r="A155" s="258"/>
       <c r="B155" s="73" t="s">
         <v>422</v>
       </c>
@@ -24689,17 +24693,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A72:A121"/>
-    <mergeCell ref="B73:B94"/>
-    <mergeCell ref="B95:B107"/>
-    <mergeCell ref="B108:B120"/>
-    <mergeCell ref="A122:A155"/>
-    <mergeCell ref="B122:B124"/>
-    <mergeCell ref="B125:B126"/>
-    <mergeCell ref="B127:B129"/>
-    <mergeCell ref="B130:B140"/>
-    <mergeCell ref="B141:B150"/>
-    <mergeCell ref="B151:B154"/>
     <mergeCell ref="C1:G3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
@@ -24714,6 +24707,17 @@
     <mergeCell ref="B57:B63"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B64:B71"/>
+    <mergeCell ref="A72:A121"/>
+    <mergeCell ref="B73:B94"/>
+    <mergeCell ref="B95:B107"/>
+    <mergeCell ref="B108:B120"/>
+    <mergeCell ref="A122:A155"/>
+    <mergeCell ref="B122:B124"/>
+    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="B127:B129"/>
+    <mergeCell ref="B130:B140"/>
+    <mergeCell ref="B141:B150"/>
+    <mergeCell ref="B151:B154"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24738,30 +24742,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="214" t="s">
+      <c r="A1" s="203" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="215"/>
-      <c r="C1" s="215"/>
-      <c r="D1" s="215"/>
-      <c r="E1" s="215"/>
-      <c r="F1" s="215"/>
-      <c r="G1" s="215"/>
-      <c r="H1" s="215"/>
-      <c r="I1" s="215"/>
-      <c r="J1" s="215"/>
-      <c r="K1" s="215"/>
-      <c r="L1" s="215"/>
-      <c r="M1" s="216"/>
+      <c r="B1" s="204"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="204"/>
+      <c r="K1" s="204"/>
+      <c r="L1" s="204"/>
+      <c r="M1" s="205"/>
     </row>
     <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="217" t="s">
+      <c r="A2" s="212" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="219" t="s">
+      <c r="B2" s="214" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="219" t="s">
+      <c r="C2" s="214" t="s">
         <v>85</v>
       </c>
       <c r="D2" s="16" t="s">
@@ -24776,29 +24780,29 @@
       <c r="G2" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="221" t="s">
+      <c r="H2" s="216" t="s">
         <v>86</v>
       </c>
-      <c r="I2" s="271" t="s">
+      <c r="I2" s="274" t="s">
         <v>88</v>
       </c>
-      <c r="J2" s="271" t="s">
+      <c r="J2" s="274" t="s">
         <v>89</v>
       </c>
-      <c r="K2" s="271" t="s">
+      <c r="K2" s="274" t="s">
         <v>90</v>
       </c>
-      <c r="L2" s="271" t="s">
+      <c r="L2" s="274" t="s">
         <v>91</v>
       </c>
-      <c r="M2" s="279" t="s">
+      <c r="M2" s="277" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="217"/>
-      <c r="B3" s="219"/>
-      <c r="C3" s="219"/>
+      <c r="A3" s="212"/>
+      <c r="B3" s="214"/>
+      <c r="C3" s="214"/>
       <c r="D3" s="16" t="str">
         <f>'Scenario overview'!B6</f>
         <v>A high-burden country close to reaching 95s across all populations</v>
@@ -24815,17 +24819,17 @@
         <f>'Scenario overview'!B9</f>
         <v>A low-burden country achieving one or more of the 95s</v>
       </c>
-      <c r="H3" s="221"/>
-      <c r="I3" s="272"/>
-      <c r="J3" s="272"/>
-      <c r="K3" s="272"/>
-      <c r="L3" s="272"/>
-      <c r="M3" s="280"/>
+      <c r="H3" s="216"/>
+      <c r="I3" s="275"/>
+      <c r="J3" s="275"/>
+      <c r="K3" s="275"/>
+      <c r="L3" s="275"/>
+      <c r="M3" s="278"/>
     </row>
     <row r="4" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="217"/>
-      <c r="B4" s="220"/>
-      <c r="C4" s="220"/>
+      <c r="A4" s="212"/>
+      <c r="B4" s="215"/>
+      <c r="C4" s="215"/>
       <c r="D4" s="31" t="str">
         <f>'Scenario overview'!C6</f>
         <v>Limited, possibly some unsuppressed ART clients and some specific sub-segments that are generally underserved</v>
@@ -24842,18 +24846,18 @@
         <f>'Scenario overview'!C9</f>
         <v>Clinically unstable/symptomatic, gaps in all population groups</v>
       </c>
-      <c r="H4" s="222"/>
-      <c r="I4" s="273"/>
-      <c r="J4" s="273"/>
-      <c r="K4" s="273"/>
-      <c r="L4" s="273"/>
-      <c r="M4" s="281"/>
+      <c r="H4" s="217"/>
+      <c r="I4" s="276"/>
+      <c r="J4" s="276"/>
+      <c r="K4" s="276"/>
+      <c r="L4" s="276"/>
+      <c r="M4" s="279"/>
     </row>
     <row r="5" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="240" t="s">
+      <c r="A5" s="257" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="211" t="s">
+      <c r="B5" s="206" t="s">
         <v>94</v>
       </c>
       <c r="C5" s="110" t="s">
@@ -24891,8 +24895,8 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="240"/>
-      <c r="B6" s="212"/>
+      <c r="A6" s="257"/>
+      <c r="B6" s="207"/>
       <c r="C6" s="96" t="s">
         <v>101</v>
       </c>
@@ -24928,8 +24932,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="31.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="240"/>
-      <c r="B7" s="212"/>
+      <c r="A7" s="257"/>
+      <c r="B7" s="207"/>
       <c r="C7" s="96" t="s">
         <v>105</v>
       </c>
@@ -24965,8 +24969,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="240"/>
-      <c r="B8" s="212"/>
+      <c r="A8" s="257"/>
+      <c r="B8" s="207"/>
       <c r="C8" s="96" t="s">
         <v>110</v>
       </c>
@@ -24998,8 +25002,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="240"/>
-      <c r="B9" s="212"/>
+      <c r="A9" s="257"/>
+      <c r="B9" s="207"/>
       <c r="C9" s="98" t="s">
         <v>113</v>
       </c>
@@ -25031,8 +25035,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="240"/>
-      <c r="B10" s="212"/>
+      <c r="A10" s="257"/>
+      <c r="B10" s="207"/>
       <c r="C10" s="98" t="s">
         <v>114</v>
       </c>
@@ -25064,8 +25068,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="240"/>
-      <c r="B11" s="212"/>
+      <c r="A11" s="257"/>
+      <c r="B11" s="207"/>
       <c r="C11" s="98" t="s">
         <v>115</v>
       </c>
@@ -25097,8 +25101,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="240"/>
-      <c r="B12" s="212"/>
+      <c r="A12" s="257"/>
+      <c r="B12" s="207"/>
       <c r="C12" s="98" t="s">
         <v>116</v>
       </c>
@@ -25134,8 +25138,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="240"/>
-      <c r="B13" s="212"/>
+      <c r="A13" s="257"/>
+      <c r="B13" s="207"/>
       <c r="C13" s="98" t="s">
         <v>117</v>
       </c>
@@ -25167,8 +25171,8 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="240"/>
-      <c r="B14" s="212"/>
+      <c r="A14" s="257"/>
+      <c r="B14" s="207"/>
       <c r="C14" s="98" t="s">
         <v>119</v>
       </c>
@@ -25204,7 +25208,7 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="61" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="240"/>
+      <c r="A15" s="257"/>
       <c r="B15" s="229"/>
       <c r="C15" s="105" t="s">
         <v>120</v>
@@ -25233,8 +25237,8 @@
       <c r="M15" s="115"/>
     </row>
     <row r="16" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="240"/>
-      <c r="B16" s="203" t="s">
+      <c r="A16" s="257"/>
+      <c r="B16" s="209" t="s">
         <v>123</v>
       </c>
       <c r="C16" s="110" t="s">
@@ -25272,8 +25276,8 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="58.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="240"/>
-      <c r="B17" s="204"/>
+      <c r="A17" s="257"/>
+      <c r="B17" s="210"/>
       <c r="C17" s="96" t="s">
         <v>128</v>
       </c>
@@ -25309,8 +25313,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="240"/>
-      <c r="B18" s="204"/>
+      <c r="A18" s="257"/>
+      <c r="B18" s="210"/>
       <c r="C18" s="96" t="s">
         <v>132</v>
       </c>
@@ -25346,8 +25350,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="31.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="240"/>
-      <c r="B19" s="204"/>
+      <c r="A19" s="257"/>
+      <c r="B19" s="210"/>
       <c r="C19" s="96" t="s">
         <v>135</v>
       </c>
@@ -25383,8 +25387,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="240"/>
-      <c r="B20" s="204"/>
+      <c r="A20" s="257"/>
+      <c r="B20" s="210"/>
       <c r="C20" s="96" t="s">
         <v>139</v>
       </c>
@@ -25420,8 +25424,8 @@
       </c>
     </row>
     <row r="21" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="240"/>
-      <c r="B21" s="205"/>
+      <c r="A21" s="257"/>
+      <c r="B21" s="218"/>
       <c r="C21" s="105" t="s">
         <v>142</v>
       </c>
@@ -25457,8 +25461,8 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="240"/>
-      <c r="B22" s="203" t="s">
+      <c r="A22" s="257"/>
+      <c r="B22" s="209" t="s">
         <v>146</v>
       </c>
       <c r="C22" s="110" t="s">
@@ -25496,8 +25500,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="240"/>
-      <c r="B23" s="204"/>
+      <c r="A23" s="257"/>
+      <c r="B23" s="210"/>
       <c r="C23" s="96" t="s">
         <v>149</v>
       </c>
@@ -25533,8 +25537,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="240"/>
-      <c r="B24" s="204"/>
+      <c r="A24" s="257"/>
+      <c r="B24" s="210"/>
       <c r="C24" s="96" t="s">
         <v>150</v>
       </c>
@@ -25570,8 +25574,8 @@
       </c>
     </row>
     <row r="25" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="240"/>
-      <c r="B25" s="204"/>
+      <c r="A25" s="257"/>
+      <c r="B25" s="210"/>
       <c r="C25" s="96" t="s">
         <v>151</v>
       </c>
@@ -25607,8 +25611,8 @@
       </c>
     </row>
     <row r="26" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="240"/>
-      <c r="B26" s="204"/>
+      <c r="A26" s="257"/>
+      <c r="B26" s="210"/>
       <c r="C26" s="96" t="s">
         <v>152</v>
       </c>
@@ -25644,8 +25648,8 @@
       </c>
     </row>
     <row r="27" spans="1:13" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="240"/>
-      <c r="B27" s="210"/>
+      <c r="A27" s="257"/>
+      <c r="B27" s="211"/>
       <c r="C27" s="157" t="s">
         <v>154</v>
       </c>
@@ -25681,8 +25685,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="240"/>
-      <c r="B28" s="203" t="s">
+      <c r="A28" s="257"/>
+      <c r="B28" s="209" t="s">
         <v>155</v>
       </c>
       <c r="C28" s="80" t="s">
@@ -25720,8 +25724,8 @@
       </c>
     </row>
     <row r="29" spans="1:13" ht="31" x14ac:dyDescent="0.2">
-      <c r="A29" s="240"/>
-      <c r="B29" s="204"/>
+      <c r="A29" s="257"/>
+      <c r="B29" s="210"/>
       <c r="C29" s="66" t="s">
         <v>158</v>
       </c>
@@ -25747,8 +25751,8 @@
       <c r="M29" s="104"/>
     </row>
     <row r="30" spans="1:13" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="240"/>
-      <c r="B30" s="204"/>
+      <c r="A30" s="257"/>
+      <c r="B30" s="210"/>
       <c r="C30" s="66" t="s">
         <v>159</v>
       </c>
@@ -25774,8 +25778,8 @@
       <c r="M30" s="104"/>
     </row>
     <row r="31" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="240"/>
-      <c r="B31" s="204"/>
+      <c r="A31" s="257"/>
+      <c r="B31" s="210"/>
       <c r="C31" s="66" t="s">
         <v>161</v>
       </c>
@@ -25801,8 +25805,8 @@
       <c r="M31" s="104"/>
     </row>
     <row r="32" spans="1:13" ht="31.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="240"/>
-      <c r="B32" s="204"/>
+      <c r="A32" s="257"/>
+      <c r="B32" s="210"/>
       <c r="C32" s="66" t="s">
         <v>162</v>
       </c>
@@ -25834,8 +25838,8 @@
       </c>
     </row>
     <row r="33" spans="1:13" ht="31.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="240"/>
-      <c r="B33" s="204"/>
+      <c r="A33" s="257"/>
+      <c r="B33" s="210"/>
       <c r="C33" s="66" t="s">
         <v>164</v>
       </c>
@@ -25867,8 +25871,8 @@
       </c>
     </row>
     <row r="34" spans="1:13" ht="32.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="240"/>
-      <c r="B34" s="204"/>
+      <c r="A34" s="257"/>
+      <c r="B34" s="210"/>
       <c r="C34" s="66" t="s">
         <v>165</v>
       </c>
@@ -25900,8 +25904,8 @@
       </c>
     </row>
     <row r="35" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="240"/>
-      <c r="B35" s="204"/>
+      <c r="A35" s="257"/>
+      <c r="B35" s="210"/>
       <c r="C35" s="66" t="s">
         <v>167</v>
       </c>
@@ -25927,8 +25931,8 @@
       <c r="M35" s="104"/>
     </row>
     <row r="36" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="240"/>
-      <c r="B36" s="204"/>
+      <c r="A36" s="257"/>
+      <c r="B36" s="210"/>
       <c r="C36" s="96" t="s">
         <v>168</v>
       </c>
@@ -25964,8 +25968,8 @@
       </c>
     </row>
     <row r="37" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="240"/>
-      <c r="B37" s="204"/>
+      <c r="A37" s="257"/>
+      <c r="B37" s="210"/>
       <c r="C37" s="98" t="s">
         <v>173</v>
       </c>
@@ -25991,8 +25995,8 @@
       <c r="M37" s="104"/>
     </row>
     <row r="38" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="240"/>
-      <c r="B38" s="205"/>
+      <c r="A38" s="257"/>
+      <c r="B38" s="218"/>
       <c r="C38" s="116" t="s">
         <v>174</v>
       </c>
@@ -26016,8 +26020,8 @@
       <c r="M38" s="117"/>
     </row>
     <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="240"/>
-      <c r="B39" s="278" t="s">
+      <c r="A39" s="257"/>
+      <c r="B39" s="273" t="s">
         <v>175</v>
       </c>
       <c r="C39" s="158" t="s">
@@ -26055,8 +26059,8 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="240"/>
-      <c r="B40" s="212"/>
+      <c r="A40" s="257"/>
+      <c r="B40" s="207"/>
       <c r="C40" s="66" t="s">
         <v>180</v>
       </c>
@@ -26086,8 +26090,8 @@
       </c>
     </row>
     <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="240"/>
-      <c r="B41" s="212"/>
+      <c r="A41" s="257"/>
+      <c r="B41" s="207"/>
       <c r="C41" s="66" t="s">
         <v>182</v>
       </c>
@@ -26123,8 +26127,8 @@
       </c>
     </row>
     <row r="42" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="240"/>
-      <c r="B42" s="212"/>
+      <c r="A42" s="257"/>
+      <c r="B42" s="207"/>
       <c r="C42" s="66" t="s">
         <v>186</v>
       </c>
@@ -26160,7 +26164,7 @@
       </c>
     </row>
     <row r="43" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="240"/>
+      <c r="A43" s="257"/>
       <c r="B43" s="229"/>
       <c r="C43" s="9" t="s">
         <v>191</v>
@@ -26197,8 +26201,8 @@
       </c>
     </row>
     <row r="44" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="240"/>
-      <c r="B44" s="269" t="s">
+      <c r="A44" s="257"/>
+      <c r="B44" s="280" t="s">
         <v>194</v>
       </c>
       <c r="C44" s="110" t="s">
@@ -26230,8 +26234,8 @@
       <c r="M44" s="118"/>
     </row>
     <row r="45" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="240"/>
-      <c r="B45" s="270"/>
+      <c r="A45" s="257"/>
+      <c r="B45" s="281"/>
       <c r="C45" s="96" t="s">
         <v>199</v>
       </c>
@@ -26267,8 +26271,8 @@
       </c>
     </row>
     <row r="46" spans="1:13" ht="31.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="240"/>
-      <c r="B46" s="270"/>
+      <c r="A46" s="257"/>
+      <c r="B46" s="281"/>
       <c r="C46" s="96" t="s">
         <v>203</v>
       </c>
@@ -26298,8 +26302,8 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="240"/>
-      <c r="B47" s="270"/>
+      <c r="A47" s="257"/>
+      <c r="B47" s="281"/>
       <c r="C47" s="96" t="s">
         <v>205</v>
       </c>
@@ -26329,8 +26333,8 @@
       </c>
     </row>
     <row r="48" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="240"/>
-      <c r="B48" s="270"/>
+      <c r="A48" s="257"/>
+      <c r="B48" s="281"/>
       <c r="C48" s="100" t="s">
         <v>206</v>
       </c>
@@ -26360,8 +26364,8 @@
       <c r="M48" s="104"/>
     </row>
     <row r="49" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="240"/>
-      <c r="B49" s="270"/>
+      <c r="A49" s="257"/>
+      <c r="B49" s="281"/>
       <c r="C49" s="96" t="s">
         <v>207</v>
       </c>
@@ -26397,8 +26401,8 @@
       </c>
     </row>
     <row r="50" spans="1:13" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="240"/>
-      <c r="B50" s="270"/>
+      <c r="A50" s="257"/>
+      <c r="B50" s="281"/>
       <c r="C50" s="157" t="s">
         <v>208</v>
       </c>
@@ -26434,8 +26438,8 @@
       </c>
     </row>
     <row r="51" spans="1:13" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="240"/>
-      <c r="B51" s="203" t="s">
+      <c r="A51" s="257"/>
+      <c r="B51" s="209" t="s">
         <v>210</v>
       </c>
       <c r="C51" s="110" t="s">
@@ -26465,8 +26469,8 @@
       <c r="M51" s="118"/>
     </row>
     <row r="52" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="240"/>
-      <c r="B52" s="204"/>
+      <c r="A52" s="257"/>
+      <c r="B52" s="210"/>
       <c r="C52" s="96" t="s">
         <v>213</v>
       </c>
@@ -26498,8 +26502,8 @@
       <c r="M52" s="104"/>
     </row>
     <row r="53" spans="1:13" ht="62.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="240"/>
-      <c r="B53" s="204"/>
+      <c r="A53" s="257"/>
+      <c r="B53" s="210"/>
       <c r="C53" s="66" t="s">
         <v>216</v>
       </c>
@@ -26515,7 +26519,7 @@
       <c r="G53" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="H53" s="206" t="s">
+      <c r="H53" s="219" t="s">
         <v>217</v>
       </c>
       <c r="I53" s="60" t="s">
@@ -26535,8 +26539,8 @@
       </c>
     </row>
     <row r="54" spans="1:13" ht="62.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="240"/>
-      <c r="B54" s="204"/>
+      <c r="A54" s="257"/>
+      <c r="B54" s="210"/>
       <c r="C54" s="66" t="s">
         <v>218</v>
       </c>
@@ -26552,7 +26556,7 @@
       <c r="G54" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="H54" s="206"/>
+      <c r="H54" s="219"/>
       <c r="I54" s="60" t="s">
         <v>483</v>
       </c>
@@ -26570,8 +26574,8 @@
       </c>
     </row>
     <row r="55" spans="1:13" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="240"/>
-      <c r="B55" s="204"/>
+      <c r="A55" s="257"/>
+      <c r="B55" s="210"/>
       <c r="C55" s="66" t="s">
         <v>219</v>
       </c>
@@ -26607,8 +26611,8 @@
       </c>
     </row>
     <row r="56" spans="1:13" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="240"/>
-      <c r="B56" s="205"/>
+      <c r="A56" s="257"/>
+      <c r="B56" s="218"/>
       <c r="C56" s="9" t="s">
         <v>427</v>
       </c>
@@ -26632,8 +26636,8 @@
       <c r="M56" s="107"/>
     </row>
     <row r="57" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="240"/>
-      <c r="B57" s="277" t="s">
+      <c r="A57" s="257"/>
+      <c r="B57" s="272" t="s">
         <v>223</v>
       </c>
       <c r="C57" s="158" t="s">
@@ -26663,8 +26667,8 @@
       <c r="M57" s="164"/>
     </row>
     <row r="58" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="240"/>
-      <c r="B58" s="204"/>
+      <c r="A58" s="257"/>
+      <c r="B58" s="210"/>
       <c r="C58" s="96" t="s">
         <v>227</v>
       </c>
@@ -26700,8 +26704,8 @@
       </c>
     </row>
     <row r="59" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="240"/>
-      <c r="B59" s="204"/>
+      <c r="A59" s="257"/>
+      <c r="B59" s="210"/>
       <c r="C59" s="96" t="s">
         <v>230</v>
       </c>
@@ -26733,8 +26737,8 @@
       </c>
     </row>
     <row r="60" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="240"/>
-      <c r="B60" s="204"/>
+      <c r="A60" s="257"/>
+      <c r="B60" s="210"/>
       <c r="C60" s="66" t="s">
         <v>232</v>
       </c>
@@ -26762,8 +26766,8 @@
       <c r="M60" s="104"/>
     </row>
     <row r="61" spans="1:13" ht="30" x14ac:dyDescent="0.2">
-      <c r="A61" s="240"/>
-      <c r="B61" s="204"/>
+      <c r="A61" s="257"/>
+      <c r="B61" s="210"/>
       <c r="C61" s="96" t="s">
         <v>235</v>
       </c>
@@ -26791,8 +26795,8 @@
       <c r="M61" s="104"/>
     </row>
     <row r="62" spans="1:13" ht="45" x14ac:dyDescent="0.2">
-      <c r="A62" s="240"/>
-      <c r="B62" s="204"/>
+      <c r="A62" s="257"/>
+      <c r="B62" s="210"/>
       <c r="C62" s="96" t="s">
         <v>236</v>
       </c>
@@ -26820,8 +26824,8 @@
       <c r="M62" s="104"/>
     </row>
     <row r="63" spans="1:13" ht="34.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="240"/>
-      <c r="B63" s="205"/>
+      <c r="A63" s="257"/>
+      <c r="B63" s="218"/>
       <c r="C63" s="152" t="s">
         <v>237</v>
       </c>
@@ -26849,8 +26853,8 @@
       <c r="M63" s="169"/>
     </row>
     <row r="64" spans="1:13" ht="114" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="240"/>
-      <c r="B64" s="274" t="s">
+      <c r="A64" s="257"/>
+      <c r="B64" s="269" t="s">
         <v>238</v>
       </c>
       <c r="C64" s="193" t="s">
@@ -26888,8 +26892,8 @@
       </c>
     </row>
     <row r="65" spans="1:13" ht="81.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="240"/>
-      <c r="B65" s="275"/>
+      <c r="A65" s="257"/>
+      <c r="B65" s="270"/>
       <c r="C65" s="194" t="s">
         <v>241</v>
       </c>
@@ -26925,8 +26929,8 @@
       </c>
     </row>
     <row r="66" spans="1:13" ht="30" x14ac:dyDescent="0.2">
-      <c r="A66" s="240"/>
-      <c r="B66" s="275"/>
+      <c r="A66" s="257"/>
+      <c r="B66" s="270"/>
       <c r="C66" s="194" t="s">
         <v>242</v>
       </c>
@@ -26954,8 +26958,8 @@
       <c r="M66" s="104"/>
     </row>
     <row r="67" spans="1:13" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="240"/>
-      <c r="B67" s="275"/>
+      <c r="A67" s="257"/>
+      <c r="B67" s="270"/>
       <c r="C67" s="194" t="s">
         <v>243</v>
       </c>
@@ -26987,8 +26991,8 @@
       </c>
     </row>
     <row r="68" spans="1:13" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="240"/>
-      <c r="B68" s="275"/>
+      <c r="A68" s="257"/>
+      <c r="B68" s="270"/>
       <c r="C68" s="194" t="s">
         <v>245</v>
       </c>
@@ -27020,8 +27024,8 @@
       </c>
     </row>
     <row r="69" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="240"/>
-      <c r="B69" s="275"/>
+      <c r="A69" s="257"/>
+      <c r="B69" s="270"/>
       <c r="C69" s="194" t="s">
         <v>247</v>
       </c>
@@ -27057,8 +27061,8 @@
       </c>
     </row>
     <row r="70" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="240"/>
-      <c r="B70" s="275"/>
+      <c r="A70" s="257"/>
+      <c r="B70" s="270"/>
       <c r="C70" s="194" t="s">
         <v>248</v>
       </c>
@@ -27094,8 +27098,8 @@
       </c>
     </row>
     <row r="71" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="241"/>
-      <c r="B71" s="276"/>
+      <c r="A71" s="258"/>
+      <c r="B71" s="271"/>
       <c r="C71" s="195" t="s">
         <v>249</v>
       </c>
@@ -27141,6 +27145,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B44:B50"/>
+    <mergeCell ref="B28:B38"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="B22:B27"/>
     <mergeCell ref="A2:A4"/>
@@ -27157,11 +27166,6 @@
     <mergeCell ref="H53:H54"/>
     <mergeCell ref="L2:L4"/>
     <mergeCell ref="M2:M4"/>
-    <mergeCell ref="B44:B50"/>
-    <mergeCell ref="B28:B38"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:G1048576 J5">
     <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
@@ -27274,6 +27278,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e236f8d0-c4c0-4f47-ae05-f87aea30adc7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="73ce610f-b889-47d4-8ab5-c38f623799c9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100814EDCEEC58F924B8688429696C030D2" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e237276d85c125e8f545490a23b9d884">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e236f8d0-c4c0-4f47-ae05-f87aea30adc7" xmlns:ns3="73ce610f-b889-47d4-8ab5-c38f623799c9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71cbdfc4356216b48f09b1dff9f37d8f" ns2:_="" ns3:_="">
     <xsd:import namespace="e236f8d0-c4c0-4f47-ae05-f87aea30adc7"/>
@@ -27534,27 +27558,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e236f8d0-c4c0-4f47-ae05-f87aea30adc7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="73ce610f-b889-47d4-8ab5-c38f623799c9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08B2BB22-8EB6-41BF-A961-2DC9DD0D7323}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06958D50-8DA8-4226-9CD9-BB7BB143D544}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e236f8d0-c4c0-4f47-ae05-f87aea30adc7"/>
+    <ds:schemaRef ds:uri="73ce610f-b889-47d4-8ab5-c38f623799c9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF1FCB26-25D5-4B69-BE24-E164640CA6E8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27571,23 +27594,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06958D50-8DA8-4226-9CD9-BB7BB143D544}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="e236f8d0-c4c0-4f47-ae05-f87aea30adc7"/>
-    <ds:schemaRef ds:uri="73ce610f-b889-47d4-8ab5-c38f623799c9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08B2BB22-8EB6-41BF-A961-2DC9DD0D7323}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>